--- a/Result/checksun_type/印刷電路板.xlsx
+++ b/Result/checksun_type/印刷電路板.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>42.55</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>42.6</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>41.46</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>41.46</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>2767.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>3043.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>3043.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>10093.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>5362.4</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>5362.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1010.262975570905</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>2767</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2767.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>42.73999999999999</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>41.42</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>41.42</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2040.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>3751.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>3751.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>10263.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>5439.54</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>5439.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-806.2180643579304</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2040</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>43.22</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>42.4</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>41.4</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2843.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>7527.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>7527</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>10587.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>5531.16</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>5531.16</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-408.0389746123274</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2843</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2843.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>43.68</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>42.32</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>41.38</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>41.38</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>4645.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>8850.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>8850</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>11384.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>5680.18</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>5680.18</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>89.32540268897355</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>4645</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4645.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>44.29</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>42.22</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>41.37</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>2921.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>10771.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>10771.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>13133.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>5760.5</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>5760.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>603.5843201662283</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>2921</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2921.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>44.69</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>41.33</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>41.33</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>6307.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>17143.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>17143.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>13297.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>5823.24</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>5823.24</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1501.397619413508</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>6307</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>6307.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>44.52</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>41.94</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>41.3</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>41.3</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>20919.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>16774.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>16774.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>13033.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>5739.88</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>5739.88</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>2367.580989073429</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>20919</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>20919.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>44.02</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>41.77</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>41.24</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>41.24</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>9458.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>13648.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>13648</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>11284.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>5386.6</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>5386.6</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>1954.857910406408</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>9458</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>9458.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>43.55</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>41.18</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>41.18</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>14252.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>13919.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>13919</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>10532.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>5296.48</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>5296.48</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>2523.401444081863</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>14252</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>14252.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>43.07</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>41.36</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>41.12</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>41.12</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>34781.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>15494.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>15494.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>9420.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>5066.56</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>5066.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>2731.842154901018</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>34781</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>34781.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>42.25000000000001</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>41.06</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>41.06</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>41.06</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>4464.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>9451.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>9451.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>6642.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>4486.98</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>4486.98</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>732.5130933962018</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>4464</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>4464.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>310.3</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>318.02</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>311.87</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>318.02</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>311.87</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2523232.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>2204640.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>2204640.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>2176774.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>2046424.68</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>2046424.68</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-76176.98089941125</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2523232</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2523232.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>308.4</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>317.98</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>312.15</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>317.98</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>312.15</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>2518700.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1978653.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>1978653.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>2145697.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>2051473.26</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>2051473.26</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-113637.4943252369</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2518700</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2518700.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>304.0</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>317.55</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>312.46</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>317.55</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>312.46</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1195817.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>2051805.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>2051805.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>2151858.4</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>2054987.16</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>2054987.16</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-162608.4601362296</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1195817</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1195817.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>306.4</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>317.2</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>313.06</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>317.2</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>313.06</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1834994.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>2358903.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>2358903.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>2231732.2</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>2094172.84</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>2094172.84</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-85022.07343278266</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1834994</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1834994.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>310.5</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>316.65</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>313.63</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>316.65</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>313.63</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>2950461.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>2318397.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>2318397.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>2298821.7</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>2163053.46</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>2163053.46</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-39631.12551954482</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>2950461</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2950461.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>311.1</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>314.68</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>314.22</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>314.68</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>314.22</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>1393297.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>2148908.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>2148908</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>2635599.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>2203334.46</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>2203334.46</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-92885.83830350684</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>1393297</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>1393297.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>311.9</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>313.92</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>314.58</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>313.92</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>314.58</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>2884459.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>2312741.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>2312741.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>2937842.5</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>2261110.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>2261110</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>1192.351944529917</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>2884459</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2884459.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>313.9</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>313.65</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>315.0</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>313.65</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>315</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>2731307.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>2251911.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>2251911.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>2994943.1</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>2265936.32</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>2265936.32</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-24220.17455629399</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>2731307</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2731307.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>313.3</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>312.18</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>314.82</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>312.18</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>314.82</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>1632465.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>2104560.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>2104560.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>3129290.7</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>2272400.34</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>2272400.34</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-43249.63475188892</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>1632465</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>1632465.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>311.7</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>311.0</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>314.82</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>311</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>314.82</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>2103012.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>2279245.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>2279245.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>3563683.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>2323172.4</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>2323172.4</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>48843.12335268594</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>2103012</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>2103012.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>310.1</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>309.85</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>314.84</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>309.85</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>314.84</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>2212464.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>3122290.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>3122290.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>3648553.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>2387265.26</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>2387265.26</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>128244.0590966255</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>2212464</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>2212464.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>40.72</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>43.4</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>48.55</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>48.55</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>35672.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>28487.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>28487</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>34170.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>41437.42</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>41437.42</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-4188.239231822641</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>35672</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>35672.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>40.2</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>43.84</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>48.81</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>48.81</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>22526.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>28958.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>28958.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>41710.4</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>41791.56</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>41791.56</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-4926.580826009347</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>22526</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>22526.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>40.13</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>44.28</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>49.14</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>49.14</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>21891.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>31912.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>31912.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>42976.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>42219.3</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>42219.3</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-4396.905216775725</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>21891</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>21891.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>40.39</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>44.72</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>49.49</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>49.49</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>29401.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>35745.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>35745.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>45604.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>42494.14</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>42494.14</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-3415.157731557134</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>29401</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>29401.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>41.22000000000001</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>45.22</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>49.87</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>49.87</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>32945.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>35478.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>35478</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>47085.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>42451.16</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>42451.16</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-2695.33426226068</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>32945</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>32945.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>42.0</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>50.22</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>50.22</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>38031.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>39853.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>39853.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>48084.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>42275.62</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>42275.62</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-1950.467368185011</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>38031</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>38031.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>43.26000000000001</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>46.31</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>46.31</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>50.6</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>37295.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>54462.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>54462</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>48707.4</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>42048.32</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>42048.32</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-1361.640827784584</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>37295</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>37295.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>43.86</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>46.83</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>50.98</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>46.83</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>50.98</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>41055.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>54040.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>54040</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>50782.7</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>41867.08</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>41867.08</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-392.9728833631088</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>41055</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>41055.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>44.1</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>47.23</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>51.32</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>47.23</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>51.32</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>28064.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>55463.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>55463.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>55843.3</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>42118.1</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>42118.1</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>602.0160687876851</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>28064</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>28064.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>44.02</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>47.57</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>51.65</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>51.65</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>54821.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>58692.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>58692.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>56745.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>43111.12</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>43111.12</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>3393.821140832108</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>54821</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>54821.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>43.98</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>47.77</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>47.77</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>52</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>111075.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>56316.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>56316.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>59575.9</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>43603.2</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>43603.2</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>4394.084774437288</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>111075</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>111075.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/印刷電路板.xlsx
+++ b/Result/checksun_type/印刷電路板.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>17.67</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1163,31 +1163,31 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.99</v>
+        <v>-0.66</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.24</v>
+        <v>-1.33</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>42.48</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>43.15</v>
+        <v>43.05</v>
       </c>
       <c r="BA2" t="n">
-        <v>42.47</v>
+        <v>42.5</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-147.29</t>
+          <t>-244.02</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-97.53</t>
+          <t>-98.47</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>77105.81458333333</t>
+          <t>77005.73509015256</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>5463.0</t>
+          <t>3299.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>2850.8</v>
+        <v>3200.8</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>2592.2</t>
+          <t>2720.2</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>5117.16</v>
+        <v>5152.92</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>480</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-477.5660753593931</t>
+          <t>-420.3601748573943</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-144.0082346945132</t>
+          <t>-105.7277220964011</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>5463.0</t>
+          <t>3299.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1646,51 +1646,51 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.7</v>
+        <v>-0.99</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.01</v>
+        <v>-1.24</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>43.19</v>
+        <v>43.15</v>
       </c>
       <c r="BA3" t="n">
-        <v>42.42</v>
+        <v>42.47</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-94.73</t>
+          <t>-147.29</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-96.62</t>
+          <t>-97.53</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>77105.81458333333</t>
+          <t>77005.73509015256</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>1331.0</t>
+          <t>5463.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>2164</v>
+        <v>2850.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>2415.9</t>
+          <t>2592.2</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>5055.46</v>
+        <v>5117.16</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-251</t>
+          <t>258</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-538.2129554802804</t>
+          <t>-477.5660753593931</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-425.4086728812981</t>
+          <t>-144.0082346945132</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>1331.0</t>
+          <t>5463.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-9.22</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2133,35 +2133,35 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.82</v>
+        <v>-0.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.68</v>
+        <v>-1.01</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>43.2</v>
+        <v>43.19</v>
       </c>
       <c r="BA4" t="n">
-        <v>42.37</v>
+        <v>42.42</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-68.56</t>
+          <t>-94.73</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-95.82</t>
+          <t>-96.62</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>77105.81458333333</t>
+          <t>77005.73509015256</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>3523.0</t>
+          <t>1331.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>2417</v>
+        <v>2164</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>2662.5</t>
+          <t>2415.9</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>5123.08</v>
+        <v>5055.46</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-245</t>
+          <t>-251</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-558.7228250437316</t>
+          <t>-538.2129554802804</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-369.5018462595149</t>
+          <t>-425.4086728812981</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>3523.0</t>
+          <t>1331.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.94</t>
+          <t>-9.22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,163 +2610,163 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.02</v>
+        <v>-0.82</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.38</v>
+        <v>-0.68</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>41.91</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-68.56</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-95.82</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>77005.73509015256</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>3523.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>2417</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>2662.5</t>
+        </is>
+      </c>
+      <c r="BM5" t="n">
+        <v>5123.08</v>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-245</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-558.7228250437316</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-369.5018462595149</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>3523.0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>宇智</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>宇智</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>43.01000000000001</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>43.17</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>42.32</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>41.91</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-48.66</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>4.39</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-95.10</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>77105.81458333333</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>2388.0</t>
-        </is>
-      </c>
-      <c r="BK5" t="n">
-        <v>2198.8</v>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>2585.0</t>
-        </is>
-      </c>
-      <c r="BM5" t="n">
-        <v>5187.66</v>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-386</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-593.1266393681346</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>-511.2955994334138</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>2388.0</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>宇智</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>宇智</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="CA5" t="inlineStr">
         <is>
           <t>-4.650682237820038</t>
@@ -2784,17 +2784,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-14.94</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,61 +3097,61 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.05</v>
+        <v>-0.38</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>43.14</t>
+          <t>43.01000000000001</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>43.12</v>
+        <v>43.17</v>
       </c>
       <c r="BA6" t="n">
-        <v>42.29</v>
+        <v>42.32</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-46.01</t>
+          <t>-48.66</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-94.51</t>
+          <t>-95.10</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>77105.81458333333</t>
+          <t>77005.73509015256</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>1549.0</t>
+          <t>2388.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>2239.6</v>
+        <v>2198.8</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>2695.6</t>
+          <t>2585.0</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>5281</v>
+        <v>5187.66</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-456</t>
+          <t>-386</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-608.0050102653566</t>
+          <t>-593.1266393681346</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-573.9904039877906</t>
+          <t>-511.2955994334138</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>1549.0</t>
+          <t>2388.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,61 +3584,61 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.74</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.19</v>
+        <v>0.05</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>43.17</t>
+          <t>43.14</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>43.09</v>
+        <v>43.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>42.28</v>
+        <v>42.29</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-39.08</t>
+          <t>-46.01</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-93.88</t>
+          <t>-94.51</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>77105.81458333333</t>
+          <t>77005.73509015256</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>2029.0</t>
+          <t>1549.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>2333.6</v>
+        <v>2239.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>2714.4</t>
+          <t>2695.6</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>5442.12</v>
+        <v>5281</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-380</t>
+          <t>-456</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-614.189484134005</t>
+          <t>-608.0050102653566</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-553.1618960659075</t>
+          <t>-573.9904039877906</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>2029.0</t>
+          <t>1549.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,61 +4071,61 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>45.98</t>
+          <t>24.33</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.09</v>
+        <v>-0.74</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.05</v>
+        <v>0.19</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>43.17</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>43.14</v>
+        <v>43.09</v>
       </c>
       <c r="BA8" t="n">
-        <v>42.26</v>
+        <v>42.28</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.89</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-29.06</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-93.28</t>
+          <t>-93.88</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>77105.81458333333</t>
+          <t>77005.73509015256</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>2596.0</t>
+          <t>2029.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>2667.8</v>
+        <v>2333.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>3095.2</t>
+          <t>2714.4</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>5561.12</v>
+        <v>5442.12</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-427</t>
+          <t>-380</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-625.2854092372954</t>
+          <t>-614.189484134005</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-555.0796741751496</t>
+          <t>-553.1618960659075</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>2596.0</t>
+          <t>2029.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,61 +4558,61 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>45.98</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.09</v>
+        <v>0.09</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>43.14</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>43.16</v>
+        <v>43.14</v>
       </c>
       <c r="BA9" t="n">
-        <v>42.2</v>
+        <v>42.26</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-29.06</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-92.79</t>
+          <t>-93.28</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>77105.81458333333</t>
+          <t>77005.73509015256</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>2432.0</t>
+          <t>2596.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>2908</v>
+        <v>2667.8</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>3046.5</t>
+          <t>3095.2</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>5561.64</v>
+        <v>5561.12</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-138</t>
+          <t>-427</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-638.0500883395038</t>
+          <t>-625.2854092372954</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-598.7450831106685</t>
+          <t>-555.0796741751496</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>2432.0</t>
+          <t>2596.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,61 +5045,61 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>70.83</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>0.99</v>
+        <v>-0.09</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>43.14</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>43.22</v>
+        <v>43.16</v>
       </c>
       <c r="BA10" t="n">
-        <v>42.15</v>
+        <v>42.2</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-23.00</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-92.29</t>
+          <t>-92.79</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>77105.81458333333</t>
+          <t>77005.73509015256</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>2592.0</t>
+          <t>2432.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>2971.2</v>
+        <v>2908</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>2993.1</t>
+          <t>3046.5</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>5575.36</v>
+        <v>5561.64</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-21</t>
+          <t>-138</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-645.1964529265648</t>
+          <t>-638.0500883395038</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-622.1690571931717</t>
+          <t>-598.7450831106685</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>2592.0</t>
+          <t>2432.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
+          <t>43.3</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
           <t>43.75</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>43.9</t>
-        </is>
-      </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5532,61 +5532,61 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>70.83</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-0.14</v>
+        <v>0.99</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.33</v>
+        <v>-0.01</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>43.25</v>
+        <v>43.22</v>
       </c>
       <c r="BA11" t="n">
-        <v>42.09</v>
+        <v>42.15</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-32.55</t>
+          <t>-23.00</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-91.85</t>
+          <t>-92.29</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>77105.81458333333</t>
+          <t>77005.73509015256</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>2019.0</t>
+          <t>2592.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>3151.6</v>
+        <v>2971.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>3015.7</t>
+          <t>2993.1</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>5534.78</v>
+        <v>5575.36</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>-21</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-649.3832521508182</t>
+          <t>-645.1964529265648</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-650.5544109827056</t>
+          <t>-622.1690571931717</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>2019.0</t>
+          <t>2592.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2944.0</t>
+          <t>2001.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.86</t>
+          <t>-33.28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>45.77</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0.62</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>-4</v>
+        <v>-3.18</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>321.5</t>
+          <t>322.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>334.9</v>
+        <v>333.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>320.76</v>
+        <v>321.29</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>319.49</t>
+          <t>319.52</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-172.52</t>
+          <t>-271.33</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.9</v>
+        <v>-1.27</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.24</v>
+        <v>0.74</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-92.79</t>
+          <t>-95.71</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1502529.235416667</t>
+          <t>1501780.524965326</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>964491.0</t>
+          <t>641806.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>1274696.2</v>
+        <v>1177470.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1927234.5</t>
+          <t>1764696.2</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>2556586.22</v>
+        <v>2550748.96</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-652538</t>
+          <t>-587225</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-188706.1746765548</t>
+          <t>-219006.4142710426</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-351277.2214749211</t>
+          <t>-385657.7320407256</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>964491.0</t>
+          <t>641806.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>328.5</t>
+          <t>324.5</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>324.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4557.0</t>
+          <t>2944.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>325.5</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-39.16</t>
+          <t>-33.86</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>2.01</v>
+        <v>0.62</v>
       </c>
       <c r="AV13" t="n">
-        <v>-4.87</v>
+        <v>-4</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>319.1</t>
+          <t>321.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>335.45</v>
+        <v>334.9</v>
       </c>
       <c r="BA13" t="n">
-        <v>320.26</v>
+        <v>320.76</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>319.48</t>
+          <t>319.49</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-143.66</t>
+          <t>-172.52</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.77</v>
+        <v>-0.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-89.68</t>
+          <t>-92.79</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1502529.235416667</t>
+          <t>1501780.524965326</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>1485179.0</t>
+          <t>964491.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>1266725.6</v>
+        <v>1274696.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>2082194.3</t>
+          <t>1927234.5</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>2560207.9</v>
+        <v>2556586.22</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-815468</t>
+          <t>-652538</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-159147.8025313973</t>
+          <t>-188706.1746765548</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-324189.9841853818</t>
+          <t>-351277.2214749211</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>1485179.0</t>
+          <t>964491.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>329.5</t>
+          <t>328.5</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>331.5</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>325.5</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5199.0</t>
+          <t>4557.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-45.44</t>
+          <t>-39.16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,12 +6988,12 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -7003,51 +7003,51 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>2.81</v>
+        <v>2.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>-5.48</v>
+        <v>-4.87</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>316.6</t>
+          <t>319.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>334.95</v>
+        <v>335.45</v>
       </c>
       <c r="BA14" t="n">
-        <v>319.43</v>
+        <v>320.26</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>319.18</t>
+          <t>319.48</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-133.52</t>
+          <t>-143.66</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.77</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.41</v>
+        <v>1.77</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-85.98</t>
+          <t>-89.68</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1502529.235416667</t>
+          <t>1501780.524965326</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>1700768.0</t>
+          <t>1485179.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>1234787.2</v>
+        <v>1266725.6</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>2263207.5</t>
+          <t>2082194.3</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>2579630.12</v>
+        <v>2560207.9</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-1028420</t>
+          <t>-815468</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-129140.1331397637</t>
+          <t>-159147.8025313973</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-329703.7171937048</t>
+          <t>-324189.9841853818</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>1700768.0</t>
+          <t>1485179.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7167,12 +7167,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,17 +7232,17 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
+          <t>329.5</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>331.5</t>
+        </is>
+      </c>
+      <c r="CS14" t="inlineStr">
+        <is>
           <t>321.0</t>
-        </is>
-      </c>
-      <c r="CR14" t="inlineStr">
-        <is>
-          <t>331.0</t>
-        </is>
-      </c>
-      <c r="CS14" t="inlineStr">
-        <is>
-          <t>320.5</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3431.0</t>
+          <t>5199.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>318.5</t>
+          <t>325.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-28.75</t>
+          <t>-45.44</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>1.21</v>
+        <v>2.81</v>
       </c>
       <c r="AV15" t="n">
-        <v>-5.91</v>
+        <v>-5.48</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>314.7</t>
+          <t>316.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>334.48</v>
+        <v>334.95</v>
       </c>
       <c r="BA15" t="n">
-        <v>319.08</v>
+        <v>319.43</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>318.9</t>
+          <t>319.18</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-126.10</t>
+          <t>-133.52</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.84</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.22</v>
+        <v>2.41</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-85.98</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1502529.235416667</t>
+          <t>1501780.524965326</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>1095110.0</t>
+          <t>1700768.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>1715281.4</v>
+        <v>1234787.2</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>2407407.4</t>
+          <t>2263207.5</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>2570986.38</v>
+        <v>2579630.12</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-692126</t>
+          <t>-1028420</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-92674.02694813808</t>
+          <t>-129140.1331397637</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-348904.1673058197</t>
+          <t>-329703.7171937048</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>1095110.0</t>
+          <t>1700768.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7654,22 +7654,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>319.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>322.0</t>
+          <t>331.0</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>316.0</t>
+          <t>320.5</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>318.5</t>
+          <t>325.5</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3578.0</t>
+          <t>3431.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>314.5</t>
+          <t>318.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-28.75</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AV16" t="n">
-        <v>-4.46</v>
+        <v>-5.91</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
+          <t>314.7</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>334.48</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>319.08</v>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
           <t>318.9</t>
         </is>
       </c>
-      <c r="AZ16" t="n">
-        <v>333.8</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>318.96</v>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>318.51</t>
-        </is>
-      </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-103.65</t>
+          <t>-126.10</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.15</v>
+        <v>-0.84</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.23</v>
+        <v>3.22</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-75.40</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1502529.235416667</t>
+          <t>1501780.524965326</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>1127933.0</t>
+          <t>1095110.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>2351921.6</v>
+        <v>1715281.4</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>2510974.0</t>
+          <t>2407407.4</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>2566859.44</v>
+        <v>2570986.38</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-159052</t>
+          <t>-692126</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-46086.72870128688</t>
+          <t>-92674.02694813808</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-298980.5900622043</t>
+          <t>-348904.1673058197</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>1127933.0</t>
+          <t>1095110.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8141,22 +8141,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>315.5</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
+          <t>322.0</t>
+        </is>
+      </c>
+      <c r="CS16" t="inlineStr">
+        <is>
+          <t>316.0</t>
+        </is>
+      </c>
+      <c r="CT16" t="inlineStr">
+        <is>
           <t>318.5</t>
-        </is>
-      </c>
-      <c r="CS16" t="inlineStr">
-        <is>
-          <t>312.0</t>
-        </is>
-      </c>
-      <c r="CT16" t="inlineStr">
-        <is>
-          <t>314.5</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2980.0</t>
+          <t>3578.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>311.5</t>
+          <t>314.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-4.62</v>
+        <v>-1.38</v>
       </c>
       <c r="AV17" t="n">
-        <v>-1.89</v>
+        <v>-4.46</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>326.6</t>
+          <t>318.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>332.9</v>
+        <v>333.8</v>
       </c>
       <c r="BA17" t="n">
-        <v>318.92</v>
+        <v>318.96</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>318.03</t>
+          <t>318.51</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-78.79</t>
+          <t>-103.65</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>1.13</v>
+        <v>-0.15</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.33</v>
+        <v>4.23</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-69.03</t>
+          <t>-75.40</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1502529.235416667</t>
+          <t>1501780.524965326</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>924638.0</t>
+          <t>1127933.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>2579772.8</v>
+        <v>2351921.6</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>2569703.8</t>
+          <t>2510974.0</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>2566882.64</v>
+        <v>2566859.44</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>-159052</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-106.0266356655411</t>
+          <t>-46086.72870128688</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-220500.0657833898</t>
+          <t>-298980.5900622043</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>924638.0</t>
+          <t>1127933.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>315.5</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>315.5</t>
+          <t>318.5</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>306.5</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>311.5</t>
+          <t>314.5</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4194.0</t>
+          <t>2980.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>311.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,12 +8936,12 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8951,51 +8951,51 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-5.61</v>
+        <v>-4.62</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.5</v>
+        <v>-1.89</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>331.6</t>
+          <t>326.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>333.25</v>
+        <v>332.9</v>
       </c>
       <c r="BA18" t="n">
-        <v>318.86</v>
+        <v>318.92</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>317.59</t>
+          <t>318.03</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-52.04</t>
+          <t>-78.79</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>3.06</v>
+        <v>1.13</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.38</v>
+        <v>5.33</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-62.93</t>
+          <t>-69.03</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1502529.235416667</t>
+          <t>1501780.524965326</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>1325487.0</t>
+          <t>924638.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>2897663</v>
+        <v>2579772.8</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>2683379.3</t>
+          <t>2569703.8</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>2605984.14</v>
+        <v>2566882.64</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>214283</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>39965.61684573888</t>
+          <t>-106.0266356655411</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-78728.42160710506</t>
+          <t>-220500.0657833898</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>1325487.0</t>
+          <t>924638.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9115,22 +9115,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>322.0</t>
+          <t>315.5</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>312.5</t>
+          <t>306.5</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>311.5</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12801.0</t>
+          <t>4194.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,177 +9242,177 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>313.0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>7.99</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>354.0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>316.0</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-1.62</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>9.36</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>320.5</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>304.0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>16.45</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025/05/22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>194.0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>-1.43</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>2025/04/28</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>316.0</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>304.0</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
         <is>
           <t>2025-10-30 00:00:00</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>354.0</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>316.0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>354.0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>320.5</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>304.0</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>-10.73</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>16.45</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025/05/22</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>194.0</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>-2.04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>2025/04/28</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>316.0</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>304.0</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,12 +9423,12 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9438,51 +9438,51 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-6.84</v>
+        <v>-5.61</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.89</v>
+        <v>-0.5</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>339.2</t>
+          <t>331.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>332.9</v>
+        <v>333.25</v>
       </c>
       <c r="BA19" t="n">
-        <v>319.19</v>
+        <v>318.86</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>317.21</t>
+          <t>317.59</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-26.14</t>
+          <t>-52.04</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>5.32</v>
+        <v>3.06</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.2</v>
+        <v>6.38</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-58.10</t>
+          <t>-62.93</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,48 +9501,48 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1502529.235416667</t>
+          <t>1501780.524965326</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>4103239.0</t>
+          <t>1325487.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>3291627.8</v>
+        <v>2897663</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>3009823.0</t>
+          <t>2683379.3</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>2621015.1</v>
+        <v>2605984.14</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>281804</t>
+          <t>214283</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>61546.35110989233</t>
+          <t>39965.61684573888</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>83666.12084498443</t>
+          <t>-78728.42160710506</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>4103239.0</t>
+          <t>1325487.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>335.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>337.0</t>
+          <t>322.0</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>307.0</t>
+          <t>312.5</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>316.0</t>
+          <t>313.0</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9704,7 +9704,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12295.0</t>
+          <t>12801.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>339.5</t>
+          <t>316.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9739,17 +9739,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-1.71</v>
+        <v>-6.84</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.1</v>
+        <v>1.89</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>345.4</t>
+          <t>339.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>331.8</v>
+        <v>332.9</v>
       </c>
       <c r="BA20" t="n">
-        <v>319.16</v>
+        <v>319.19</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>316.88</t>
+          <t>317.21</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-26.14</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>7.83</v>
+        <v>5.32</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.68</v>
+        <v>7.2</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-55.37</t>
+          <t>-58.10</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>1502529.235416667</t>
+          <t>1501780.524965326</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>4278311.0</t>
+          <t>4103239.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>3099533.4</v>
+        <v>3291627.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>3157022.2</t>
+          <t>3009823.0</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>2554484.6</v>
+        <v>2621015.1</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-57488</t>
+          <t>281804</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>57524.57479442105</t>
+          <t>61546.35110989233</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>15053.96288921963</t>
+          <t>83666.12084498443</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>4278311.0</t>
+          <t>4103239.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>347.0</t>
+          <t>335.5</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>362.5</t>
+          <t>337.0</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>336.0</t>
+          <t>307.0</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>339.5</t>
+          <t>316.0</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6546.0</t>
+          <t>12295.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>353.0</t>
+          <t>339.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-21.13</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>81.13</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>46.72</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>2.68</v>
+        <v>-1.71</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.97</v>
+        <v>4.1</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>343.8</t>
+          <t>345.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>330.68</v>
+        <v>331.8</v>
       </c>
       <c r="BA21" t="n">
-        <v>318.69</v>
+        <v>319.16</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>316.58</t>
+          <t>316.88</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>11.55</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>8.52</v>
+        <v>7.83</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.64</v>
+        <v>7.68</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-55.59</t>
+          <t>-55.37</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>1502529.235416667</t>
+          <t>1501780.524965326</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>2267189.0</t>
+          <t>4278311.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>2670026.4</v>
+        <v>3099533.4</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>3385442.4</t>
+          <t>3157022.2</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>2497804.86</v>
+        <v>2554484.6</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-715416</t>
+          <t>-57488</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>65246.50423173039</t>
+          <t>57524.57479442105</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-102258.7614364885</t>
+          <t>15053.96288921963</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>2267189.0</t>
+          <t>4278311.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,12 +10641,12 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>340.5</t>
+          <t>347.0</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>354.5</t>
+          <t>362.5</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>353.0</t>
+          <t>339.5</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8858.0</t>
+          <t>11279.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10718,12 +10718,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>30.30</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-63.49</t>
+          <t>-63.07</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10858,22 +10858,22 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-06-20 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,12 +10884,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10903,47 +10903,47 @@
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>9.699999999999999</v>
+        <v>5.54</v>
       </c>
       <c r="AV22" t="n">
-        <v>18.59</v>
+        <v>22.31</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>55.23999999999999</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>46.58</v>
+        <v>47.48</v>
       </c>
       <c r="BA22" t="n">
-        <v>45.89</v>
+        <v>46.11</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>142.06</t>
+          <t>105.80</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>3.42</v>
+        <v>3.96</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-89.62</t>
+          <t>-85.89</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>718764.2937500001</t>
+          <t>719235.1976421637</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>531651.0</t>
+          <t>705524.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>665029.6</v>
+        <v>770207.6</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>523057.5</t>
+          <t>591103.1</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>135986.22</v>
+        <v>149283.02</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>141972</t>
+          <t>179104</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>76510.45465103655</t>
+          <t>84047.64808930038</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>133449.7914191877</t>
+          <t>125502.2119997515</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>531651.0</t>
+          <t>705524.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,22 +11063,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>255.42</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
+          <t>65.1</t>
+        </is>
+      </c>
+      <c r="CS22" t="inlineStr">
+        <is>
+          <t>58.6</t>
+        </is>
+      </c>
+      <c r="CT22" t="inlineStr">
+        <is>
           <t>61.3</t>
-        </is>
-      </c>
-      <c r="CS22" t="inlineStr">
-        <is>
-          <t>58.4</t>
-        </is>
-      </c>
-      <c r="CT22" t="inlineStr">
-        <is>
-          <t>60.6</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21925.0</t>
+          <t>8858.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>27.14</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-63.98</t>
+          <t>-63.49</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11345,22 +11345,22 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-06-20 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>53.61</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11390,47 +11390,47 @@
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>13.88</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AV23" t="n">
-        <v>14.94</v>
+        <v>18.59</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-7.00</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>52.51000000000001</t>
+          <t>55.23999999999999</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>45.68</v>
+        <v>46.58</v>
       </c>
       <c r="BA23" t="n">
-        <v>45.66</v>
+        <v>45.89</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>203.00</t>
+          <t>142.06</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>2.76</v>
+        <v>3.42</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.91</v>
+        <v>1.41</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-93.31</t>
+          <t>-89.62</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>718764.2937500001</t>
+          <t>719235.1976421637</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>1307789.0</t>
+          <t>531651.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>613317.8</v>
+        <v>665029.6</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>472603.9</t>
+          <t>523057.5</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>125932.14</v>
+        <v>135986.22</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>140713</t>
+          <t>141972</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>66157.84796591816</t>
+          <t>76510.45465103655</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>158666.66232484</t>
+          <t>133449.7914191877</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>1307789.0</t>
+          <t>531651.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>255.42</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11652,7 +11652,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>17344.0</t>
+          <t>21925.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>74.90</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-65.72</t>
+          <t>-63.98</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11832,38 +11832,38 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2025-06-20 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>53.61</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11873,51 +11873,51 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>88.55</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>12.34</v>
+        <v>13.88</v>
       </c>
       <c r="AV24" t="n">
-        <v>13.02</v>
+        <v>14.94</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.00</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>52.51000000000001</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>44.82</v>
+        <v>45.68</v>
       </c>
       <c r="BA24" t="n">
-        <v>45.45</v>
+        <v>45.66</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>49.11</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>336.90</t>
+          <t>203.00</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>1.96</v>
+        <v>2.76</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-96.70</t>
+          <t>-93.31</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>718764.2937500001</t>
+          <t>719235.1976421637</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>951271.0</t>
+          <t>1307789.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>601649</v>
+        <v>613317.8</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>343989.9</t>
+          <t>472603.9</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>100400.3</v>
+        <v>125932.14</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>257659</t>
+          <t>140713</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>49338.06353702328</t>
+          <t>66157.84796591816</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>105866.4542498846</t>
+          <t>158666.66232484</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>951271.0</t>
+          <t>1307789.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>255.42</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7063.0</t>
+          <t>17344.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>82.91</t>
+          <t>74.90</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-68.80</t>
+          <t>-65.72</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12319,22 +12319,22 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2025-06-20 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>17.27</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12360,51 +12360,51 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>88.55</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>5.13</v>
+        <v>12.34</v>
       </c>
       <c r="AV25" t="n">
-        <v>11.96</v>
+        <v>13.02</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-7.86</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>50.65</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>44.01</v>
+        <v>44.82</v>
       </c>
       <c r="BA25" t="n">
-        <v>45.31</v>
+        <v>45.45</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>49.18</t>
+          <t>49.11</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>1603.09</t>
+          <t>336.90</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>1.21</v>
+        <v>1.96</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-99.48</t>
+          <t>-96.70</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>718764.2937500001</t>
+          <t>719235.1976421637</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>354803.0</t>
+          <t>951271.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>460316.6</v>
+        <v>601649</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>251659.1</t>
+          <t>343989.9</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>82011.2</v>
+        <v>100400.3</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>208657</t>
+          <t>257659</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>39060.17431650303</t>
+          <t>49338.06353702328</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>64854.99791959545</t>
+          <t>105866.4542498846</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>354803.0</t>
+          <t>951271.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,22 +12524,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>255.42</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3819.0</t>
+          <t>7063.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>88.28</t>
+          <t>82.91</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-71.63</t>
+          <t>-68.80</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12806,22 +12806,22 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2025-06-20 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>17.27</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,17 +12832,17 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>65.66</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
@@ -12851,47 +12851,47 @@
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-1.9</v>
+        <v>5.13</v>
       </c>
       <c r="AV26" t="n">
-        <v>10.54</v>
+        <v>11.96</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-7.86</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>48.01000000000001</t>
+          <t>49.27</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>43.43</v>
+        <v>44.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>45.28</v>
+        <v>45.31</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.18</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>449.01</t>
+          <t>1603.09</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.74</v>
+        <v>1.21</v>
       </c>
       <c r="BE26" t="n">
-        <v>-0.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-101.56</t>
+          <t>-99.48</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>718764.2937500001</t>
+          <t>719235.1976421637</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>179634.0</t>
+          <t>354803.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>411998.6</v>
+        <v>460316.6</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>218827.9</t>
+          <t>251659.1</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>75776.96000000001</v>
+        <v>82011.2</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>193170</t>
+          <t>208657</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>34370.20638866805</t>
+          <t>39060.17431650303</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>67858.23895062532</t>
+          <t>64854.99791959545</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>179634.0</t>
+          <t>354803.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-21.24</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,22 +13011,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>255.42</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-7.1</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5696.0</t>
+          <t>3819.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>23.16</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>88.22</t>
+          <t>88.28</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-71.72</t>
+          <t>-71.63</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13293,22 +13293,22 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2025-06-20 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>64.14</t>
+          <t>65.66</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>88.05</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>0.17</v>
+        <v>-1.9</v>
       </c>
       <c r="AV27" t="n">
-        <v>8.890000000000001</v>
+        <v>10.54</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-8.15</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>46.87</t>
+          <t>48.01000000000001</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>43.04</v>
+        <v>43.43</v>
       </c>
       <c r="BA27" t="n">
-        <v>45.34</v>
+        <v>45.28</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>49.48</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>237.21</t>
+          <t>449.01</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="BE27" t="n">
-        <v>-0.45</v>
+        <v>-0.21</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-103.32</t>
+          <t>-101.56</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>718764.2937500001</t>
+          <t>719235.1976421637</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>273092.0</t>
+          <t>179634.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>381085.4</v>
+        <v>411998.6</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>202472.5</t>
+          <t>218827.9</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>73397</v>
+        <v>75776.96000000001</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>178612</t>
+          <t>193170</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>28281.47319558491</t>
+          <t>34370.20638866805</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>88493.18188957428</t>
+          <t>67858.23895062532</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>273092.0</t>
+          <t>179634.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-21.49</t>
+          <t>-21.24</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,12 +13498,12 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>255.42</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-7.1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>23888.0</t>
+          <t>5696.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>88.22</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-69.58</t>
+          <t>-71.72</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13780,22 +13780,22 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2025-06-20 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>64.14</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.05</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>10.75</v>
+        <v>0.17</v>
       </c>
       <c r="AV28" t="n">
-        <v>6.7</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>46.87</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>42.74</v>
+        <v>43.04</v>
       </c>
       <c r="BA28" t="n">
-        <v>45.46</v>
+        <v>45.34</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>49.48</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>165.19</t>
+          <t>237.21</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.47</v>
+        <v>0.62</v>
       </c>
       <c r="BE28" t="n">
-        <v>-0.72</v>
+        <v>-0.45</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-105.29</t>
+          <t>-103.32</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>718764.2937500001</t>
+          <t>719235.1976421637</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>1249445.0</t>
+          <t>273092.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>331890</v>
+        <v>381085.4</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>177274.1</t>
+          <t>202472.5</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>68543.64</v>
+        <v>73397</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>154615</t>
+          <t>178612</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>17333.88979667774</t>
+          <t>28281.47319558491</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>104797.8438777308</t>
+          <t>88493.18188957428</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>1249445.0</t>
+          <t>273092.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-15.55</t>
+          <t>-21.49</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,22 +13985,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>255.42</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4930.0</t>
+          <t>23888.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17.49</t>
+          <t>17.62</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>62.27</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-69.88</t>
+          <t>-69.58</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -14267,22 +14267,22 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2025-06-20 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>58.41</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -14293,12 +14293,12 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -14308,51 +14308,51 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>78.01</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU29" t="n">
-        <v>14.42</v>
+        <v>10.75</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.55</v>
+        <v>6.7</v>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>-7.2</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>42.2</v>
+        <v>42.74</v>
       </c>
       <c r="BA29" t="n">
-        <v>45.48</v>
+        <v>45.46</v>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>91.04</t>
+          <t>165.19</t>
         </is>
       </c>
       <c r="BD29" t="n">
-        <v>-0.09</v>
+        <v>0.47</v>
       </c>
       <c r="BE29" t="n">
-        <v>-1.02</v>
+        <v>-0.72</v>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>-107.47</t>
+          <t>-105.29</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -14371,43 +14371,43 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>718764.2937500001</t>
+          <t>719235.1976421637</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>244609.0</t>
+          <t>1249445.0</t>
         </is>
       </c>
       <c r="BK29" t="n">
-        <v>86330.8</v>
+        <v>331890</v>
       </c>
       <c r="BL29" t="inlineStr">
         <is>
-          <t>53201.3</t>
+          <t>177274.1</t>
         </is>
       </c>
       <c r="BM29" t="n">
-        <v>43961.4</v>
+        <v>68543.64</v>
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>33129</t>
+          <t>154615</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>1431.352691031731</t>
+          <t>17333.88979667774</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>19738.18800803549</t>
+          <t>104797.8438777308</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>244609.0</t>
+          <t>1249445.0</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="BU29" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-15.55</t>
         </is>
       </c>
       <c r="BV29" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="CI29" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>255.42</t>
         </is>
       </c>
       <c r="CJ29" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="CN29" t="inlineStr">
@@ -14537,22 +14537,22 @@
       </c>
       <c r="CQ29" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CR29" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CT29" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CU29" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2538.0</t>
+          <t>4930.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -14609,17 +14609,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>62.27</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-72.59</t>
+          <t>-69.88</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -14754,22 +14754,22 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2025-06-20 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -14780,12 +14780,12 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -14795,51 +14795,51 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>78.01</t>
         </is>
       </c>
       <c r="AU30" t="n">
-        <v>7.82</v>
+        <v>14.42</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.14</v>
+        <v>3.55</v>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-7.2</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>41.72</v>
+        <v>42.2</v>
       </c>
       <c r="BA30" t="n">
-        <v>45.51</v>
+        <v>45.48</v>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>39.60</t>
+          <t>91.04</t>
         </is>
       </c>
       <c r="BD30" t="n">
-        <v>-0.75</v>
+        <v>-0.09</v>
       </c>
       <c r="BE30" t="n">
-        <v>-1.25</v>
+        <v>-1.02</v>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>-109.17</t>
+          <t>-107.47</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -14858,43 +14858,43 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>718764.2937500001</t>
+          <t>719235.1976421637</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>113213.0</t>
+          <t>244609.0</t>
         </is>
       </c>
       <c r="BK30" t="n">
-        <v>43001.6</v>
+        <v>86330.8</v>
       </c>
       <c r="BL30" t="inlineStr">
         <is>
-          <t>30209.8</t>
+          <t>53201.3</t>
         </is>
       </c>
       <c r="BM30" t="n">
-        <v>39457.08</v>
+        <v>43961.4</v>
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>-1897.16282115077</t>
+          <t>1431.352691031731</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>5180.458622469465</t>
+          <t>19738.18800803549</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>113213.0</t>
+          <t>244609.0</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="BU30" t="inlineStr">
         <is>
-          <t>-23.91</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="BV30" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="CI30" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>255.42</t>
         </is>
       </c>
       <c r="CJ30" t="inlineStr">
@@ -14999,12 +14999,12 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="CN30" t="inlineStr">
@@ -15024,22 +15024,22 @@
       </c>
       <c r="CQ30" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CT30" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CU30" t="inlineStr">
@@ -15071,12 +15071,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>2538.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -15096,17 +15096,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-75.06</t>
+          <t>-72.59</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -15241,22 +15241,22 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2025-06-20 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -15267,66 +15267,66 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="AU31" t="n">
-        <v>-0.7</v>
+        <v>7.82</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.39</v>
+        <v>1.14</v>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>-9.0</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>-8.92</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>41.53</v>
+        <v>41.72</v>
       </c>
       <c r="BA31" t="n">
-        <v>45.64</v>
+        <v>45.51</v>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>39.60</t>
         </is>
       </c>
       <c r="BD31" t="n">
-        <v>-1.13</v>
+        <v>-0.75</v>
       </c>
       <c r="BE31" t="n">
-        <v>-1.37</v>
+        <v>-1.25</v>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>-110.08</t>
+          <t>-109.17</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -15345,43 +15345,43 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>718764.2937500001</t>
+          <t>719235.1976421637</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
         <is>
-          <t>25068.0</t>
+          <t>113213.0</t>
         </is>
       </c>
       <c r="BK31" t="n">
-        <v>25657.2</v>
+        <v>43001.6</v>
       </c>
       <c r="BL31" t="inlineStr">
         <is>
-          <t>20953.7</t>
+          <t>30209.8</t>
         </is>
       </c>
       <c r="BM31" t="n">
-        <v>37685.12</v>
+        <v>39457.08</v>
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>12791</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>-3184.003083627177</t>
+          <t>-1897.16282115077</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>-1723.17116485591</t>
+          <t>5180.458622469465</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>25068.0</t>
+          <t>113213.0</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="BU31" t="inlineStr">
         <is>
-          <t>-30.77</t>
+          <t>-23.91</t>
         </is>
       </c>
       <c r="BV31" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
@@ -15456,12 +15456,12 @@
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="CI31" t="inlineStr">
         <is>
-          <t>252.5</t>
+          <t>255.42</t>
         </is>
       </c>
       <c r="CJ31" t="inlineStr">
@@ -15486,12 +15486,12 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>267.8</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="CN31" t="inlineStr">
@@ -15511,22 +15511,22 @@
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CR31" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CT31" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CU31" t="inlineStr">

--- a/Result/checksun_type/印刷電路板.xlsx
+++ b/Result/checksun_type/印刷電路板.xlsx
@@ -948,42 +948,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-1.43</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>41.6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>42.2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1163,47 +1163,47 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.66</v>
+        <v>-1.42</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.33</v>
+        <v>-1.77</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>43.05</v>
+        <v>42.96</v>
       </c>
       <c r="BA2" t="n">
-        <v>42.5</v>
+        <v>42.52</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-244.02</t>
+          <t>-1098.80</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.1</v>
+        <v>-0.18</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-98.47</t>
+          <t>-99.59</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>77005.73509015256</t>
+          <t>76909.03878116343</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>3299.0</t>
+          <t>4794.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>3200.8</v>
+        <v>3682</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>2720.2</t>
+          <t>2940.4</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>5152.92</v>
+        <v>5156.86</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>741</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-420.3601748573943</t>
+          <t>-350.1760202986125</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-105.7277220964011</t>
+          <t>35.83682977468789</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>3299.0</t>
+          <t>4794.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-1.44</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>17.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1650,31 +1650,31 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.99</v>
+        <v>-0.66</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.24</v>
+        <v>-1.33</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>42.48</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>43.15</v>
+        <v>43.05</v>
       </c>
       <c r="BA3" t="n">
-        <v>42.47</v>
+        <v>42.5</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-147.29</t>
+          <t>-244.02</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-97.53</t>
+          <t>-98.47</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>77005.73509015256</t>
+          <t>76909.03878116343</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>5463.0</t>
+          <t>3299.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>2850.8</v>
+        <v>3200.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>2592.2</t>
+          <t>2720.2</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>5117.16</v>
+        <v>5152.92</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>480</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-477.5660753593931</t>
+          <t>-420.3601748573943</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-144.0082346945132</t>
+          <t>-105.7277220964011</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>5463.0</t>
+          <t>3299.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2133,51 +2133,51 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.7</v>
+        <v>-0.99</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1.01</v>
+        <v>-1.24</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>43.19</v>
+        <v>43.15</v>
       </c>
       <c r="BA4" t="n">
-        <v>42.42</v>
+        <v>42.47</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-94.73</t>
+          <t>-147.29</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-96.62</t>
+          <t>-97.53</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>77005.73509015256</t>
+          <t>76909.03878116343</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>1331.0</t>
+          <t>5463.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>2164</v>
+        <v>2850.8</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>2415.9</t>
+          <t>2592.2</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>5055.46</v>
+        <v>5117.16</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-251</t>
+          <t>258</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-538.2129554802804</t>
+          <t>-477.5660753593931</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-425.4086728812981</t>
+          <t>-144.0082346945132</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>1331.0</t>
+          <t>5463.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2302,17 +2302,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-9.22</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2620,35 +2620,35 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.82</v>
+        <v>-0.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.68</v>
+        <v>-1.01</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>43.2</v>
+        <v>43.19</v>
       </c>
       <c r="BA5" t="n">
-        <v>42.37</v>
+        <v>42.42</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-68.56</t>
+          <t>-94.73</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-95.82</t>
+          <t>-96.62</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>77005.73509015256</t>
+          <t>76909.03878116343</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>3523.0</t>
+          <t>1331.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>2417</v>
+        <v>2164</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>2662.5</t>
+          <t>2415.9</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>5123.08</v>
+        <v>5055.46</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-245</t>
+          <t>-251</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-558.7228250437316</t>
+          <t>-538.2129554802804</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-369.5018462595149</t>
+          <t>-425.4086728812981</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>3523.0</t>
+          <t>1331.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-14.94</t>
+          <t>-9.22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,163 +3097,163 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.02</v>
+        <v>-0.82</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.38</v>
+        <v>-0.68</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>41.91</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-68.56</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-95.82</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>76909.03878116343</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>3523.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="n">
+        <v>2417</v>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>2662.5</t>
+        </is>
+      </c>
+      <c r="BM6" t="n">
+        <v>5123.08</v>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-245</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-558.7228250437316</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-369.5018462595149</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>3523.0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>宇智</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>宇智</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>43.01000000000001</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>43.17</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>42.32</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>41.91</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-48.66</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>4.39</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-95.10</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>77005.73509015256</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>2388.0</t>
-        </is>
-      </c>
-      <c r="BK6" t="n">
-        <v>2198.8</v>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>2585.0</t>
-        </is>
-      </c>
-      <c r="BM6" t="n">
-        <v>5187.66</v>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-386</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-593.1266393681346</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>-511.2955994334138</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>2388.0</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>宇智</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>宇智</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="CA6" t="inlineStr">
         <is>
           <t>-4.650682237820038</t>
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-14.94</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,61 +3584,61 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.05</v>
+        <v>-0.38</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>43.14</t>
+          <t>43.01000000000001</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>43.12</v>
+        <v>43.17</v>
       </c>
       <c r="BA7" t="n">
-        <v>42.29</v>
+        <v>42.32</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-46.01</t>
+          <t>-48.66</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-94.51</t>
+          <t>-95.10</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>77005.73509015256</t>
+          <t>76909.03878116343</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>1549.0</t>
+          <t>2388.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>2239.6</v>
+        <v>2198.8</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>2695.6</t>
+          <t>2585.0</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>5281</v>
+        <v>5187.66</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-456</t>
+          <t>-386</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-608.0050102653566</t>
+          <t>-593.1266393681346</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-573.9904039877906</t>
+          <t>-511.2955994334138</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>1549.0</t>
+          <t>2388.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,61 +4071,61 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.74</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.19</v>
+        <v>0.05</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>43.17</t>
+          <t>43.14</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>43.09</v>
+        <v>43.12</v>
       </c>
       <c r="BA8" t="n">
-        <v>42.28</v>
+        <v>42.29</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-39.08</t>
+          <t>-46.01</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-93.88</t>
+          <t>-94.51</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>77005.73509015256</t>
+          <t>76909.03878116343</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>2029.0</t>
+          <t>1549.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>2333.6</v>
+        <v>2239.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>2714.4</t>
+          <t>2695.6</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>5442.12</v>
+        <v>5281</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-380</t>
+          <t>-456</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-614.189484134005</t>
+          <t>-608.0050102653566</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-553.1618960659075</t>
+          <t>-573.9904039877906</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>2029.0</t>
+          <t>1549.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,61 +4558,61 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>45.98</t>
+          <t>24.33</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0.09</v>
+        <v>-0.74</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.05</v>
+        <v>0.19</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>43.17</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>43.14</v>
+        <v>43.09</v>
       </c>
       <c r="BA9" t="n">
-        <v>42.26</v>
+        <v>42.28</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.89</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-29.06</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-93.28</t>
+          <t>-93.88</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>77005.73509015256</t>
+          <t>76909.03878116343</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>2596.0</t>
+          <t>2029.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>2667.8</v>
+        <v>2333.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>3095.2</t>
+          <t>2714.4</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>5561.12</v>
+        <v>5442.12</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-427</t>
+          <t>-380</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-625.2854092372954</t>
+          <t>-614.189484134005</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-555.0796741751496</t>
+          <t>-553.1618960659075</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>2596.0</t>
+          <t>2029.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,61 +5045,61 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>45.98</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.09</v>
+        <v>0.09</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>43.14</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>43.16</v>
+        <v>43.14</v>
       </c>
       <c r="BA10" t="n">
-        <v>42.2</v>
+        <v>42.26</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-29.06</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-92.79</t>
+          <t>-93.28</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>77005.73509015256</t>
+          <t>76909.03878116343</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>2432.0</t>
+          <t>2596.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>2908</v>
+        <v>2667.8</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>3046.5</t>
+          <t>3095.2</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>5561.64</v>
+        <v>5561.12</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-138</t>
+          <t>-427</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-638.0500883395038</t>
+          <t>-625.2854092372954</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-598.7450831106685</t>
+          <t>-555.0796741751496</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>2432.0</t>
+          <t>2596.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5532,61 +5532,61 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>70.83</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>0.99</v>
+        <v>-0.09</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>43.14</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>43.22</v>
+        <v>43.16</v>
       </c>
       <c r="BA11" t="n">
-        <v>42.15</v>
+        <v>42.2</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-23.00</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-92.29</t>
+          <t>-92.79</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>77005.73509015256</t>
+          <t>76909.03878116343</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>2592.0</t>
+          <t>2432.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>2971.2</v>
+        <v>2908</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>2993.1</t>
+          <t>3046.5</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>5575.36</v>
+        <v>5561.64</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-21</t>
+          <t>-138</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-645.1964529265648</t>
+          <t>-638.0500883395038</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-622.1690571931717</t>
+          <t>-598.7450831106685</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>2592.0</t>
+          <t>2432.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
+          <t>43.3</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
           <t>43.75</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>43.9</t>
-        </is>
-      </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2001.0</t>
+          <t>1510.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.28</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>60.71</t>
+          <t>53.57</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.15</v>
       </c>
       <c r="AV12" t="n">
-        <v>-3.18</v>
+        <v>-2.36</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>322.6</t>
+          <t>322.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>333.2</v>
+        <v>330.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>321.29</v>
+        <v>321.92</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>319.52</t>
+          <t>319.66</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-271.33</t>
+          <t>-705.26</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-1.27</v>
+        <v>-1.62</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.74</v>
+        <v>0.27</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-95.71</t>
+          <t>-98.45</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1501780.524965326</t>
+          <t>1500700.784626039</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>641806.0</t>
+          <t>481472.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>1177470.8</v>
+        <v>1054743.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1764696.2</t>
+          <t>1385012.3</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>2550748.96</v>
+        <v>2545738.9</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-587225</t>
+          <t>-330269</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-219006.4142710426</t>
+          <t>-248714.3037886931</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-385657.7320407256</t>
+          <t>-412107.6961357708</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>641806.0</t>
+          <t>481472.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>80.18</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>324.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>324.5</t>
+          <t>321.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>318.0</t>
+          <t>316.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2944.0</t>
+          <t>2001.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-33.86</t>
+          <t>-33.28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>45.77</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>0.62</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>-4</v>
+        <v>-3.18</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>321.5</t>
+          <t>322.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>334.9</v>
+        <v>333.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>320.76</v>
+        <v>321.29</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>319.49</t>
+          <t>319.52</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-172.52</t>
+          <t>-271.33</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.9</v>
+        <v>-1.27</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.24</v>
+        <v>0.74</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-92.79</t>
+          <t>-95.71</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1501780.524965326</t>
+          <t>1500700.784626039</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>964491.0</t>
+          <t>641806.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>1274696.2</v>
+        <v>1177470.8</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1927234.5</t>
+          <t>1764696.2</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>2556586.22</v>
+        <v>2550748.96</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-652538</t>
+          <t>-587225</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-188706.1746765548</t>
+          <t>-219006.4142710426</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-351277.2214749211</t>
+          <t>-385657.7320407256</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>964491.0</t>
+          <t>641806.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>80.18</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>328.5</t>
+          <t>324.5</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>324.5</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4557.0</t>
+          <t>2944.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>325.5</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-39.16</t>
+          <t>-33.86</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>2.01</v>
+        <v>0.62</v>
       </c>
       <c r="AV14" t="n">
-        <v>-4.87</v>
+        <v>-4</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>319.1</t>
+          <t>321.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>335.45</v>
+        <v>334.9</v>
       </c>
       <c r="BA14" t="n">
-        <v>320.26</v>
+        <v>320.76</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>319.48</t>
+          <t>319.49</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-143.66</t>
+          <t>-172.52</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.77</v>
+        <v>-0.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-89.68</t>
+          <t>-92.79</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1501780.524965326</t>
+          <t>1500700.784626039</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>1485179.0</t>
+          <t>964491.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>1266725.6</v>
+        <v>1274696.2</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>2082194.3</t>
+          <t>1927234.5</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>2560207.9</v>
+        <v>2556586.22</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-815468</t>
+          <t>-652538</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-159147.8025313973</t>
+          <t>-188706.1746765548</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-324189.9841853818</t>
+          <t>-351277.2214749211</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>1485179.0</t>
+          <t>964491.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>80.18</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>329.5</t>
+          <t>328.5</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>331.5</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>325.5</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5199.0</t>
+          <t>4557.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-45.44</t>
+          <t>-39.16</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,12 +7475,12 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -7490,51 +7490,51 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>2.81</v>
+        <v>2.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>-5.48</v>
+        <v>-4.87</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>316.6</t>
+          <t>319.1</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>334.95</v>
+        <v>335.45</v>
       </c>
       <c r="BA15" t="n">
-        <v>319.43</v>
+        <v>320.26</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>319.18</t>
+          <t>319.48</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-133.52</t>
+          <t>-143.66</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.77</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.41</v>
+        <v>1.77</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-85.98</t>
+          <t>-89.68</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1501780.524965326</t>
+          <t>1500700.784626039</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>1700768.0</t>
+          <t>1485179.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>1234787.2</v>
+        <v>1266725.6</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>2263207.5</t>
+          <t>2082194.3</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>2579630.12</v>
+        <v>2560207.9</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-1028420</t>
+          <t>-815468</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-129140.1331397637</t>
+          <t>-159147.8025313973</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-329703.7171937048</t>
+          <t>-324189.9841853818</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>1700768.0</t>
+          <t>1485179.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>80.18</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,17 +7719,17 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
+          <t>329.5</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>331.5</t>
+        </is>
+      </c>
+      <c r="CS15" t="inlineStr">
+        <is>
           <t>321.0</t>
-        </is>
-      </c>
-      <c r="CR15" t="inlineStr">
-        <is>
-          <t>331.0</t>
-        </is>
-      </c>
-      <c r="CS15" t="inlineStr">
-        <is>
-          <t>320.5</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3431.0</t>
+          <t>5199.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>318.5</t>
+          <t>325.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-28.75</t>
+          <t>-45.44</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>1.21</v>
+        <v>2.81</v>
       </c>
       <c r="AV16" t="n">
-        <v>-5.91</v>
+        <v>-5.48</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>314.7</t>
+          <t>316.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>334.48</v>
+        <v>334.95</v>
       </c>
       <c r="BA16" t="n">
-        <v>319.08</v>
+        <v>319.43</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>318.9</t>
+          <t>319.18</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-126.10</t>
+          <t>-133.52</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.84</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.22</v>
+        <v>2.41</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-85.98</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1501780.524965326</t>
+          <t>1500700.784626039</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>1095110.0</t>
+          <t>1700768.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>1715281.4</v>
+        <v>1234787.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>2407407.4</t>
+          <t>2263207.5</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>2570986.38</v>
+        <v>2579630.12</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-692126</t>
+          <t>-1028420</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-92674.02694813808</t>
+          <t>-129140.1331397637</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-348904.1673058197</t>
+          <t>-329703.7171937048</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>1095110.0</t>
+          <t>1700768.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,17 +8141,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>80.18</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>319.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>322.0</t>
+          <t>331.0</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>316.0</t>
+          <t>320.5</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>318.5</t>
+          <t>325.5</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3578.0</t>
+          <t>3431.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>314.5</t>
+          <t>318.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-28.75</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AV17" t="n">
-        <v>-4.46</v>
+        <v>-5.91</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
+          <t>314.7</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>334.48</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>319.08</v>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
           <t>318.9</t>
         </is>
       </c>
-      <c r="AZ17" t="n">
-        <v>333.8</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>318.96</v>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>318.51</t>
-        </is>
-      </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-103.65</t>
+          <t>-126.10</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.15</v>
+        <v>-0.84</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.23</v>
+        <v>3.22</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-75.40</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1501780.524965326</t>
+          <t>1500700.784626039</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>1127933.0</t>
+          <t>1095110.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>2351921.6</v>
+        <v>1715281.4</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>2510974.0</t>
+          <t>2407407.4</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>2566859.44</v>
+        <v>2570986.38</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-159052</t>
+          <t>-692126</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-46086.72870128688</t>
+          <t>-92674.02694813808</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-298980.5900622043</t>
+          <t>-348904.1673058197</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>1127933.0</t>
+          <t>1095110.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,17 +8628,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>80.18</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>315.5</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
+          <t>322.0</t>
+        </is>
+      </c>
+      <c r="CS17" t="inlineStr">
+        <is>
+          <t>316.0</t>
+        </is>
+      </c>
+      <c r="CT17" t="inlineStr">
+        <is>
           <t>318.5</t>
-        </is>
-      </c>
-      <c r="CS17" t="inlineStr">
-        <is>
-          <t>312.0</t>
-        </is>
-      </c>
-      <c r="CT17" t="inlineStr">
-        <is>
-          <t>314.5</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2980.0</t>
+          <t>3578.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>311.5</t>
+          <t>314.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-4.62</v>
+        <v>-1.38</v>
       </c>
       <c r="AV18" t="n">
-        <v>-1.89</v>
+        <v>-4.46</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>326.6</t>
+          <t>318.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>332.9</v>
+        <v>333.8</v>
       </c>
       <c r="BA18" t="n">
-        <v>318.92</v>
+        <v>318.96</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>318.03</t>
+          <t>318.51</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-78.79</t>
+          <t>-103.65</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>1.13</v>
+        <v>-0.15</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.33</v>
+        <v>4.23</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-69.03</t>
+          <t>-75.40</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1501780.524965326</t>
+          <t>1500700.784626039</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>924638.0</t>
+          <t>1127933.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>2579772.8</v>
+        <v>2351921.6</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>2569703.8</t>
+          <t>2510974.0</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>2566882.64</v>
+        <v>2566859.44</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>-159052</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-106.0266356655411</t>
+          <t>-46086.72870128688</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-220500.0657833898</t>
+          <t>-298980.5900622043</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>924638.0</t>
+          <t>1127933.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>80.18</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>315.5</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>315.5</t>
+          <t>318.5</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>306.5</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>311.5</t>
+          <t>314.5</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4194.0</t>
+          <t>2980.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>311.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,12 +9423,12 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9438,51 +9438,51 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-5.61</v>
+        <v>-4.62</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.5</v>
+        <v>-1.89</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>331.6</t>
+          <t>326.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>333.25</v>
+        <v>332.9</v>
       </c>
       <c r="BA19" t="n">
-        <v>318.86</v>
+        <v>318.92</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>317.59</t>
+          <t>318.03</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-52.04</t>
+          <t>-78.79</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>3.06</v>
+        <v>1.13</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.38</v>
+        <v>5.33</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-62.93</t>
+          <t>-69.03</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1501780.524965326</t>
+          <t>1500700.784626039</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>1325487.0</t>
+          <t>924638.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>2897663</v>
+        <v>2579772.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>2683379.3</t>
+          <t>2569703.8</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>2605984.14</v>
+        <v>2566882.64</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>214283</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>39965.61684573888</t>
+          <t>-106.0266356655411</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-78728.42160710506</t>
+          <t>-220500.0657833898</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>1325487.0</t>
+          <t>924638.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>80.18</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>322.0</t>
+          <t>315.5</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>312.5</t>
+          <t>306.5</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>311.5</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12801.0</t>
+          <t>4194.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,177 +9729,177 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>313.0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>7.99</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>354.0</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>316.0</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-1.33</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>9.36</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>320.5</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>304.0</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>16.45</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025/05/22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>194.0</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>-1.43</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2025/04/28</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>316.0</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>304.0</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
         <is>
           <t>2025-10-30 00:00:00</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>354.0</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>316.0</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>354.0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>320.5</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>304.0</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>-10.73</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>16.45</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025/05/22</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>194.0</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>-2.04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>2025/04/28</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>316.0</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>304.0</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,12 +9910,12 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -9925,51 +9925,51 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-6.84</v>
+        <v>-5.61</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.89</v>
+        <v>-0.5</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>339.2</t>
+          <t>331.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>332.9</v>
+        <v>333.25</v>
       </c>
       <c r="BA20" t="n">
-        <v>319.19</v>
+        <v>318.86</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>317.21</t>
+          <t>317.59</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-26.14</t>
+          <t>-52.04</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>5.32</v>
+        <v>3.06</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.2</v>
+        <v>6.38</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-58.10</t>
+          <t>-62.93</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,48 +9988,48 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>1501780.524965326</t>
+          <t>1500700.784626039</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>4103239.0</t>
+          <t>1325487.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>3291627.8</v>
+        <v>2897663</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>3009823.0</t>
+          <t>2683379.3</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>2621015.1</v>
+        <v>2605984.14</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>281804</t>
+          <t>214283</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>61546.35110989233</t>
+          <t>39965.61684573888</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>83666.12084498443</t>
+          <t>-78728.42160710506</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>4103239.0</t>
+          <t>1325487.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>80.18</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>335.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>337.0</t>
+          <t>322.0</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>307.0</t>
+          <t>312.5</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>316.0</t>
+          <t>313.0</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10191,7 +10191,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12295.0</t>
+          <t>12801.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>339.5</t>
+          <t>316.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-1.71</v>
+        <v>-6.84</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.1</v>
+        <v>1.89</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>345.4</t>
+          <t>339.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>331.8</v>
+        <v>332.9</v>
       </c>
       <c r="BA21" t="n">
-        <v>319.16</v>
+        <v>319.19</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>316.88</t>
+          <t>317.21</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-26.14</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>7.83</v>
+        <v>5.32</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.68</v>
+        <v>7.2</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-55.37</t>
+          <t>-58.10</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>1501780.524965326</t>
+          <t>1500700.784626039</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>4278311.0</t>
+          <t>4103239.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>3099533.4</v>
+        <v>3291627.8</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>3157022.2</t>
+          <t>3009823.0</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>2554484.6</v>
+        <v>2621015.1</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-57488</t>
+          <t>281804</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>57524.57479442105</t>
+          <t>61546.35110989233</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>15053.96288921963</t>
+          <t>83666.12084498443</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>4278311.0</t>
+          <t>4103239.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>80.18</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>347.0</t>
+          <t>335.5</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>362.5</t>
+          <t>337.0</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>336.0</t>
+          <t>307.0</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>339.5</t>
+          <t>316.0</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11279.0</t>
+          <t>5174.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10718,12 +10718,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>30.30</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,33 +10863,33 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10903,47 +10903,47 @@
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>5.54</v>
+        <v>2.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>22.31</v>
+        <v>23.89</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>47.48</v>
+        <v>48.42</v>
       </c>
       <c r="BA22" t="n">
-        <v>46.11</v>
+        <v>46.35</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>105.80</t>
+          <t>80.10</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>3.96</v>
+        <v>4.33</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-85.89</t>
+          <t>-82.35</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>719235.1976421637</t>
+          <t>718898.358033241</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>705524.0</t>
+          <t>317358.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>770207.6</v>
+        <v>762718.6</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>591103.1</t>
+          <t>611517.6</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>149283.02</v>
+        <v>155195.8</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>179104</t>
+          <t>151201</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>84047.64808930038</t>
+          <t>84607.84086112375</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>125502.2119997515</t>
+          <t>87688.90110615233</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>705524.0</t>
+          <t>317358.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
@@ -11128,17 +11128,17 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8858.0</t>
+          <t>11279.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>30.30</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-63.49</t>
+          <t>-63.07</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11390,47 +11390,47 @@
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>9.699999999999999</v>
+        <v>5.54</v>
       </c>
       <c r="AV23" t="n">
-        <v>18.59</v>
+        <v>22.31</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>55.23999999999999</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>46.58</v>
+        <v>47.48</v>
       </c>
       <c r="BA23" t="n">
-        <v>45.89</v>
+        <v>46.11</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>142.06</t>
+          <t>105.80</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>3.42</v>
+        <v>3.96</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-89.62</t>
+          <t>-85.89</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>719235.1976421637</t>
+          <t>718898.358033241</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>531651.0</t>
+          <t>705524.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>665029.6</v>
+        <v>770207.6</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>523057.5</t>
+          <t>591103.1</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>135986.22</v>
+        <v>149283.02</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>141972</t>
+          <t>179104</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>76510.45465103655</t>
+          <t>84047.64808930038</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>133449.7914191877</t>
+          <t>125502.2119997515</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>531651.0</t>
+          <t>705524.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,17 +11550,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
+          <t>65.1</t>
+        </is>
+      </c>
+      <c r="CS23" t="inlineStr">
+        <is>
+          <t>58.6</t>
+        </is>
+      </c>
+      <c r="CT23" t="inlineStr">
+        <is>
           <t>61.3</t>
-        </is>
-      </c>
-      <c r="CS23" t="inlineStr">
-        <is>
-          <t>58.4</t>
-        </is>
-      </c>
-      <c r="CT23" t="inlineStr">
-        <is>
-          <t>60.6</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21925.0</t>
+          <t>8858.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>27.14</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-63.98</t>
+          <t>-63.49</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>53.61</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11877,47 +11877,47 @@
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>13.88</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AV24" t="n">
-        <v>14.94</v>
+        <v>18.59</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-7.00</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>52.51000000000001</t>
+          <t>55.23999999999999</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>45.68</v>
+        <v>46.58</v>
       </c>
       <c r="BA24" t="n">
-        <v>45.66</v>
+        <v>45.89</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>203.00</t>
+          <t>142.06</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>2.76</v>
+        <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.91</v>
+        <v>1.41</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-93.31</t>
+          <t>-89.62</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>719235.1976421637</t>
+          <t>718898.358033241</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>1307789.0</t>
+          <t>531651.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>613317.8</v>
+        <v>665029.6</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>472603.9</t>
+          <t>523057.5</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>125932.14</v>
+        <v>135986.22</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>140713</t>
+          <t>141972</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>66157.84796591816</t>
+          <t>76510.45465103655</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>158666.66232484</t>
+          <t>133449.7914191877</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>1307789.0</t>
+          <t>531651.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,17 +12037,17 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17344.0</t>
+          <t>21925.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>74.90</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-65.72</t>
+          <t>-63.98</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,33 +12324,33 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>53.61</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12360,51 +12360,51 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>88.55</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>12.34</v>
+        <v>13.88</v>
       </c>
       <c r="AV25" t="n">
-        <v>13.02</v>
+        <v>14.94</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.00</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>52.51000000000001</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>44.82</v>
+        <v>45.68</v>
       </c>
       <c r="BA25" t="n">
-        <v>45.45</v>
+        <v>45.66</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>49.11</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>336.90</t>
+          <t>203.00</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>1.96</v>
+        <v>2.76</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-96.70</t>
+          <t>-93.31</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>719235.1976421637</t>
+          <t>718898.358033241</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>951271.0</t>
+          <t>1307789.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>601649</v>
+        <v>613317.8</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>343989.9</t>
+          <t>472603.9</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>100400.3</v>
+        <v>125932.14</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>257659</t>
+          <t>140713</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>49338.06353702328</t>
+          <t>66157.84796591816</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>105866.4542498846</t>
+          <t>158666.66232484</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>951271.0</t>
+          <t>1307789.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7063.0</t>
+          <t>17344.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>82.91</t>
+          <t>74.90</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-68.80</t>
+          <t>-65.72</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>17.27</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12847,51 +12847,51 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>88.55</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>5.13</v>
+        <v>12.34</v>
       </c>
       <c r="AV26" t="n">
-        <v>11.96</v>
+        <v>13.02</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-7.86</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>50.65</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>44.01</v>
+        <v>44.82</v>
       </c>
       <c r="BA26" t="n">
-        <v>45.31</v>
+        <v>45.45</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>49.18</t>
+          <t>49.11</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>1603.09</t>
+          <t>336.90</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>1.21</v>
+        <v>1.96</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-99.48</t>
+          <t>-96.70</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>719235.1976421637</t>
+          <t>718898.358033241</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>354803.0</t>
+          <t>951271.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>460316.6</v>
+        <v>601649</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>251659.1</t>
+          <t>343989.9</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>82011.2</v>
+        <v>100400.3</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>208657</t>
+          <t>257659</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>39060.17431650303</t>
+          <t>49338.06353702328</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>64854.99791959545</t>
+          <t>105866.4542498846</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>354803.0</t>
+          <t>951271.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3819.0</t>
+          <t>7063.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>88.28</t>
+          <t>82.91</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-71.63</t>
+          <t>-68.80</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>17.27</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,17 +13319,17 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>65.66</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
@@ -13338,47 +13338,47 @@
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-1.9</v>
+        <v>5.13</v>
       </c>
       <c r="AV27" t="n">
-        <v>10.54</v>
+        <v>11.96</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-7.86</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>48.01000000000001</t>
+          <t>49.27</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>43.43</v>
+        <v>44.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>45.28</v>
+        <v>45.31</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.18</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>449.01</t>
+          <t>1603.09</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.74</v>
+        <v>1.21</v>
       </c>
       <c r="BE27" t="n">
-        <v>-0.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-101.56</t>
+          <t>-99.48</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>719235.1976421637</t>
+          <t>718898.358033241</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>179634.0</t>
+          <t>354803.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>411998.6</v>
+        <v>460316.6</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>218827.9</t>
+          <t>251659.1</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>75776.96000000001</v>
+        <v>82011.2</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>193170</t>
+          <t>208657</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>34370.20638866805</t>
+          <t>39060.17431650303</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>67858.23895062532</t>
+          <t>64854.99791959545</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>179634.0</t>
+          <t>354803.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-21.24</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,17 +13498,17 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-7.1</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5696.0</t>
+          <t>3819.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>23.16</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>88.22</t>
+          <t>88.28</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-71.72</t>
+          <t>-71.63</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>64.14</t>
+          <t>65.66</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>88.05</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>0.17</v>
+        <v>-1.9</v>
       </c>
       <c r="AV28" t="n">
-        <v>8.890000000000001</v>
+        <v>10.54</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-8.15</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>46.87</t>
+          <t>48.01000000000001</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>43.04</v>
+        <v>43.43</v>
       </c>
       <c r="BA28" t="n">
-        <v>45.34</v>
+        <v>45.28</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>49.48</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>237.21</t>
+          <t>449.01</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="BE28" t="n">
-        <v>-0.45</v>
+        <v>-0.21</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-103.32</t>
+          <t>-101.56</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>719235.1976421637</t>
+          <t>718898.358033241</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>273092.0</t>
+          <t>179634.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>381085.4</v>
+        <v>411998.6</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>202472.5</t>
+          <t>218827.9</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>73397</v>
+        <v>75776.96000000001</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>178612</t>
+          <t>193170</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>28281.47319558491</t>
+          <t>34370.20638866805</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>88493.18188957428</t>
+          <t>67858.23895062532</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>273092.0</t>
+          <t>179634.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-21.49</t>
+          <t>-21.24</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,12 +13985,12 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-7.1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>23888.0</t>
+          <t>5696.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>88.22</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-69.58</t>
+          <t>-71.72</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -14272,17 +14272,17 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -14293,66 +14293,66 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>64.14</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.05</t>
         </is>
       </c>
       <c r="AU29" t="n">
-        <v>10.75</v>
+        <v>0.17</v>
       </c>
       <c r="AV29" t="n">
-        <v>6.7</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>46.87</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>42.74</v>
+        <v>43.04</v>
       </c>
       <c r="BA29" t="n">
-        <v>45.46</v>
+        <v>45.34</v>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>49.48</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>165.19</t>
+          <t>237.21</t>
         </is>
       </c>
       <c r="BD29" t="n">
-        <v>0.47</v>
+        <v>0.62</v>
       </c>
       <c r="BE29" t="n">
-        <v>-0.72</v>
+        <v>-0.45</v>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>-105.29</t>
+          <t>-103.32</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -14371,43 +14371,43 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>719235.1976421637</t>
+          <t>718898.358033241</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>1249445.0</t>
+          <t>273092.0</t>
         </is>
       </c>
       <c r="BK29" t="n">
-        <v>331890</v>
+        <v>381085.4</v>
       </c>
       <c r="BL29" t="inlineStr">
         <is>
-          <t>177274.1</t>
+          <t>202472.5</t>
         </is>
       </c>
       <c r="BM29" t="n">
-        <v>68543.64</v>
+        <v>73397</v>
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>154615</t>
+          <t>178612</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>17333.88979667774</t>
+          <t>28281.47319558491</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>104797.8438777308</t>
+          <t>88493.18188957428</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>1249445.0</t>
+          <t>273092.0</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="BU29" t="inlineStr">
         <is>
-          <t>-15.55</t>
+          <t>-21.49</t>
         </is>
       </c>
       <c r="BV29" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
@@ -14537,22 +14537,22 @@
       </c>
       <c r="CQ29" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CR29" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CT29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CU29" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4930.0</t>
+          <t>23888.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -14609,17 +14609,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>17.62</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>62.27</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-69.88</t>
+          <t>-69.58</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -14759,17 +14759,17 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>58.41</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -14780,12 +14780,12 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -14795,51 +14795,51 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>78.01</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU30" t="n">
-        <v>14.42</v>
+        <v>10.75</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.55</v>
+        <v>6.7</v>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>-7.2</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>42.2</v>
+        <v>42.74</v>
       </c>
       <c r="BA30" t="n">
-        <v>45.48</v>
+        <v>45.46</v>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>91.04</t>
+          <t>165.19</t>
         </is>
       </c>
       <c r="BD30" t="n">
-        <v>-0.09</v>
+        <v>0.47</v>
       </c>
       <c r="BE30" t="n">
-        <v>-1.02</v>
+        <v>-0.72</v>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>-107.47</t>
+          <t>-105.29</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -14858,43 +14858,43 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>719235.1976421637</t>
+          <t>718898.358033241</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>244609.0</t>
+          <t>1249445.0</t>
         </is>
       </c>
       <c r="BK30" t="n">
-        <v>86330.8</v>
+        <v>331890</v>
       </c>
       <c r="BL30" t="inlineStr">
         <is>
-          <t>53201.3</t>
+          <t>177274.1</t>
         </is>
       </c>
       <c r="BM30" t="n">
-        <v>43961.4</v>
+        <v>68543.64</v>
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>33129</t>
+          <t>154615</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>1431.352691031731</t>
+          <t>17333.88979667774</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>19738.18800803549</t>
+          <t>104797.8438777308</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>244609.0</t>
+          <t>1249445.0</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="BU30" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-15.55</t>
         </is>
       </c>
       <c r="BV30" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
@@ -15024,22 +15024,22 @@
       </c>
       <c r="CQ30" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CT30" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CU30" t="inlineStr">
@@ -15071,12 +15071,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2538.0</t>
+          <t>4930.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -15096,17 +15096,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>62.27</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-72.59</t>
+          <t>-69.88</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -15246,17 +15246,17 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -15267,12 +15267,12 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -15282,51 +15282,51 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>78.01</t>
         </is>
       </c>
       <c r="AU31" t="n">
-        <v>7.82</v>
+        <v>14.42</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.14</v>
+        <v>3.55</v>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-7.2</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>41.72</v>
+        <v>42.2</v>
       </c>
       <c r="BA31" t="n">
-        <v>45.51</v>
+        <v>45.48</v>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>39.60</t>
+          <t>91.04</t>
         </is>
       </c>
       <c r="BD31" t="n">
-        <v>-0.75</v>
+        <v>-0.09</v>
       </c>
       <c r="BE31" t="n">
-        <v>-1.25</v>
+        <v>-1.02</v>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>-109.17</t>
+          <t>-107.47</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -15345,43 +15345,43 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>719235.1976421637</t>
+          <t>718898.358033241</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
         <is>
-          <t>113213.0</t>
+          <t>244609.0</t>
         </is>
       </c>
       <c r="BK31" t="n">
-        <v>43001.6</v>
+        <v>86330.8</v>
       </c>
       <c r="BL31" t="inlineStr">
         <is>
-          <t>30209.8</t>
+          <t>53201.3</t>
         </is>
       </c>
       <c r="BM31" t="n">
-        <v>39457.08</v>
+        <v>43961.4</v>
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>-1897.16282115077</t>
+          <t>1431.352691031731</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>5180.458622469465</t>
+          <t>19738.18800803549</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>113213.0</t>
+          <t>244609.0</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="BU31" t="inlineStr">
         <is>
-          <t>-23.91</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="BV31" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>260.07</t>
+          <t>263.62</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
@@ -15511,22 +15511,22 @@
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CR31" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CT31" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CU31" t="inlineStr">

--- a/Result/checksun_type/印刷電路板.xlsx
+++ b/Result/checksun_type/印刷電路板.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1118,22 +1118,22 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,45 +1149,45 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>67.86</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.41</v>
+        <v>1.45</v>
       </c>
       <c r="AV2" t="n">
-        <v>-2.21</v>
+        <v>-1.88</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>42.82</v>
+        <v>42.74</v>
       </c>
       <c r="BA2" t="n">
-        <v>42.55</v>
+        <v>42.58</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -1196,23 +1196,23 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-237.95</t>
+          <t>-109.73</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.28</v>
+        <v>-0.24</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-106.26</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>16485.2381443299</t>
+          <t>76619.90689655172</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>4588.0</t>
+          <t>7093.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>4106.8</v>
+        <v>4432.8</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>3135.4</t>
+          <t>3641.8</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>5210.02</v>
+        <v>5324.22</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>791</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-247.1599272691658</t>
+          <t>-159.2021487908879</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>62.27217885235677</t>
+          <t>324.5656328396403</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>4588.0</t>
+          <t>7093.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1308,37 +1308,37 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>-4.650682237820038</t>
+          <t>-2.035038170073544</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>-31.92659851902614</t>
+          <t>-22.78705596482432</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>6.977755118136152</t>
+          <t>3.962846154661839</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,92 +1535,92 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-18.18</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>46.1</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/04/11</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>43.8</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>42.05</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2024-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>7.59</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
           <t>-0.60</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-18.18</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>46.1</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/04/11</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>42.05</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>3.93</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>-0.36</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,45 +1636,45 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
           <t>3.57</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
       <c r="AU3" t="n">
-        <v>-0.88</v>
+        <v>-0.41</v>
       </c>
       <c r="AV3" t="n">
-        <v>-2.02</v>
+        <v>-2.21</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>42.89</v>
+        <v>42.82</v>
       </c>
       <c r="BA3" t="n">
-        <v>42.53</v>
+        <v>42.55</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -1683,23 +1683,23 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-616.22</t>
+          <t>-237.95</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-102.54</t>
+          <t>-101.87</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>16485.2381443299</t>
+          <t>76619.90689655172</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>2390.0</t>
+          <t>4588.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>3455.4</v>
+        <v>4106.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>2936.2</t>
+          <t>3135.4</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>5165.48</v>
+        <v>5210.02</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>971</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-303.4203102003517</t>
+          <t>-247.1599272691658</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-46.26390465991744</t>
+          <t>62.27217885235677</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>2390.0</t>
+          <t>4588.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>-4.650682237820038</t>
+          <t>-2.035038170073544</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>-31.92659851902614</t>
+          <t>-22.78705596482432</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>6.977755118136152</t>
+          <t>3.962846154661839</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
+          <t>41.65</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>42.05</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
           <t>41.6</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>41.85</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
-      </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2092,22 +2092,22 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,45 +2123,45 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.42</v>
+        <v>-0.88</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1.77</v>
+        <v>-2.02</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>42.96</v>
+        <v>42.89</v>
       </c>
       <c r="BA4" t="n">
-        <v>42.52</v>
+        <v>42.53</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -2170,23 +2170,23 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1098.80</t>
+          <t>-616.22</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.18</v>
+        <v>-0.24</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-98.63</t>
+          <t>-100.76</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>16485.2381443299</t>
+          <t>76619.90689655172</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>4794.0</t>
+          <t>2390.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>3682</v>
+        <v>3455.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>2940.4</t>
+          <t>2936.2</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>5156.86</v>
+        <v>5165.48</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>519</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-350.1760202986125</t>
+          <t>-303.4203102003517</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>35.83682977468789</t>
+          <t>-46.26390465991744</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>4794.0</t>
+          <t>2390.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2282,27 +2282,27 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>-4.650682237820038</t>
+          <t>-2.035038170073544</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-31.92659851902614</t>
+          <t>-22.78705596482432</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>6.977755118136152</t>
+          <t>3.962846154661839</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-1.43</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>41.6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>42.2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2579,22 +2579,22 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2624,56 +2624,56 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.66</v>
+        <v>-1.42</v>
       </c>
       <c r="AV5" t="n">
-        <v>-1.33</v>
+        <v>-1.77</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>43.05</v>
+        <v>42.96</v>
       </c>
       <c r="BA5" t="n">
-        <v>42.5</v>
+        <v>42.52</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-244.02</t>
+          <t>-1098.80</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.1</v>
+        <v>-0.18</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-94.86</t>
+          <t>-99.59</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>16485.2381443299</t>
+          <t>76619.90689655172</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>3299.0</t>
+          <t>4794.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>3200.8</v>
+        <v>3682</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>2720.2</t>
+          <t>2940.4</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>5152.92</v>
+        <v>5156.86</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>741</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-420.3601748573943</t>
+          <t>-350.1760202986125</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-105.7277220964011</t>
+          <t>35.83682977468789</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>3299.0</t>
+          <t>4794.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2769,37 +2769,37 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>-4.650682237820038</t>
+          <t>-2.035038170073544</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-31.92659851902614</t>
+          <t>-22.78705596482432</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>6.977755118136152</t>
+          <t>3.962846154661839</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>17.67</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3066,22 +3066,22 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3111,31 +3111,31 @@
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.99</v>
+        <v>-0.66</v>
       </c>
       <c r="AV6" t="n">
-        <v>-1.24</v>
+        <v>-1.33</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>42.48</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>43.16</v>
+        <v>43.05</v>
       </c>
       <c r="BA6" t="n">
-        <v>42.47</v>
+        <v>42.5</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -3144,23 +3144,23 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-147.29</t>
+          <t>-244.02</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-91.73</t>
+          <t>-98.47</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>16485.2381443299</t>
+          <t>76619.90689655172</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>5463.0</t>
+          <t>3299.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>2850.8</v>
+        <v>3200.8</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>2592.2</t>
+          <t>2720.2</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>5117.16</v>
+        <v>5152.92</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>480</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-477.5660753593931</t>
+          <t>-420.3601748573943</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-144.0082346945132</t>
+          <t>-105.7277220964011</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>5463.0</t>
+          <t>3299.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3256,27 +3256,27 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>-4.650682237820038</t>
+          <t>-2.035038170073544</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-31.92659851902614</t>
+          <t>-22.78705596482432</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>6.977755118136152</t>
+          <t>3.962846154661839</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,17 +3336,17 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3553,22 +3553,22 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3594,60 +3594,60 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.7</v>
+        <v>-0.99</v>
       </c>
       <c r="AV7" t="n">
-        <v>-1.01</v>
+        <v>-1.24</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>43.19</v>
+        <v>43.15</v>
       </c>
       <c r="BA7" t="n">
-        <v>42.42</v>
+        <v>42.47</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-94.73</t>
+          <t>-147.29</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-88.68</t>
+          <t>-97.53</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>16485.2381443299</t>
+          <t>76619.90689655172</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>1331.0</t>
+          <t>5463.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>2164</v>
+        <v>2850.8</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>2415.9</t>
+          <t>2592.2</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>5055.46</v>
+        <v>5117.16</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-251</t>
+          <t>258</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-538.2129554802804</t>
+          <t>-477.5660753593931</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-425.4086728812981</t>
+          <t>-144.0082346945132</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>1331.0</t>
+          <t>5463.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3743,17 +3743,17 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>-4.650682237820038</t>
+          <t>-2.035038170073544</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-31.92659851902614</t>
+          <t>-22.78705596482432</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>6.977755118136152</t>
+          <t>3.962846154661839</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3763,17 +3763,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-9.22</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4081,35 +4081,35 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.82</v>
+        <v>-0.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.68</v>
+        <v>-1.01</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>43.2</v>
+        <v>43.19</v>
       </c>
       <c r="BA8" t="n">
-        <v>42.37</v>
+        <v>42.42</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
@@ -4118,23 +4118,23 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-68.56</t>
+          <t>-94.73</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-86.00</t>
+          <t>-96.62</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>16485.2381443299</t>
+          <t>76619.90689655172</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>3523.0</t>
+          <t>1331.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>2417</v>
+        <v>2164</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>2662.5</t>
+          <t>2415.9</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>5123.08</v>
+        <v>5055.46</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-245</t>
+          <t>-251</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-558.7228250437316</t>
+          <t>-538.2129554802804</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-369.5018462595149</t>
+          <t>-425.4086728812981</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>3523.0</t>
+          <t>1331.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4230,22 +4230,22 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>-4.650682237820038</t>
+          <t>-2.035038170073544</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-31.92659851902614</t>
+          <t>-22.78705596482432</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>6.977755118136152</t>
+          <t>3.962846154661839</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.94</t>
+          <t>-9.22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4527,22 +4527,22 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,181 +4558,181 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.02</v>
+        <v>-0.82</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.38</v>
+        <v>-0.68</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>41.91</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-68.56</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-95.82</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>76619.90689655172</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>3523.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="n">
+        <v>2417</v>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>2662.5</t>
+        </is>
+      </c>
+      <c r="BM9" t="n">
+        <v>5123.08</v>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-245</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-558.7228250437316</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-369.5018462595149</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>3523.0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>宇智</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>宇智</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>43.01000000000001</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>43.17</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>42.32</v>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>41.91</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-48.66</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-83.60</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>16485.2381443299</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>2388.0</t>
-        </is>
-      </c>
-      <c r="BK9" t="n">
-        <v>2198.8</v>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>2585.0</t>
-        </is>
-      </c>
-      <c r="BM9" t="n">
-        <v>5187.66</v>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-386</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-593.1266393681346</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-511.2955994334138</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>2388.0</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>宇智</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>宇智</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>-4.650682237820038</t>
+          <t>-2.035038170073544</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-31.92659851902614</t>
+          <t>-22.78705596482432</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>6.977755118136152</t>
+          <t>3.962846154661839</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-14.94</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,70 +5045,70 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.05</v>
+        <v>-0.38</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>43.14</t>
+          <t>43.01000000000001</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>43.12</v>
+        <v>43.17</v>
       </c>
       <c r="BA10" t="n">
-        <v>42.29</v>
+        <v>42.32</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-46.01</t>
+          <t>-48.66</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-81.61</t>
+          <t>-95.10</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>16485.2381443299</t>
+          <t>76619.90689655172</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>1549.0</t>
+          <t>2388.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>2239.6</v>
+        <v>2198.8</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>2695.6</t>
+          <t>2585.0</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>5281</v>
+        <v>5187.66</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-456</t>
+          <t>-386</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-608.0050102653566</t>
+          <t>-593.1266393681346</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-573.9904039877906</t>
+          <t>-511.2955994334138</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>1549.0</t>
+          <t>2388.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5204,22 +5204,22 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>-4.650682237820038</t>
+          <t>-2.035038170073544</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>-31.92659851902614</t>
+          <t>-22.78705596482432</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>6.977755118136152</t>
+          <t>3.962846154661839</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4451.0</t>
+          <t>3223.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5501,22 +5501,22 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-10-31 00:00:00</t>
+          <t>2025-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,12 +5527,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>135</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5542,51 +5542,51 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-2.74</v>
+        <v>-2.87</v>
       </c>
       <c r="AV11" t="n">
-        <v>-2.88</v>
+        <v>-3.61</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>317.7</t>
+          <t>314.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>327.12</v>
+        <v>325.75</v>
       </c>
       <c r="BA11" t="n">
-        <v>322.85</v>
+        <v>323.37</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>319.5</t>
+          <t>318.96</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-296.96</t>
+          <t>-185.73</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-2.98</v>
+        <v>-4</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.75</v>
+        <v>-1.4</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-104.36</t>
+          <t>-108.14</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>1939682.155670103</t>
+          <t>1503043.582758621</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>1386639.0</t>
+          <t>986882.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>1046928.2</v>
+        <v>1051406.4</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1156826.9</t>
+          <t>1163051.3</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>2577472.64</v>
+        <v>2582295.04</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-109898</t>
+          <t>-111644</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-263833.401299818</t>
+          <t>-265829.8268954243</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-282935.7762331311</t>
+          <t>-276810.167671259</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>1386639.0</t>
+          <t>986882.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,27 +5686,27 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>-8.972382204888667</t>
+          <t>0.8245111470917923</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>146.345773861391</t>
+          <t>135.4246787601293</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>132.2935565532715</t>
+          <t>132.6458021161182</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>81.24</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>28730</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>319.0</t>
+          <t>311.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>314.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>307.5</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5448.0</t>
+          <t>4451.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>317.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5988,22 +5988,22 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-10-31 00:00:00</t>
+          <t>2025-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>135</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>51.19</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.25</v>
+        <v>-2.74</v>
       </c>
       <c r="AV12" t="n">
-        <v>-2.27</v>
+        <v>-2.88</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>317.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>328.45</v>
+        <v>327.12</v>
       </c>
       <c r="BA12" t="n">
-        <v>322.49</v>
+        <v>322.85</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>319.69</t>
+          <t>319.5</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-953.47</t>
+          <t>-296.96</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-2.03</v>
+        <v>-2.98</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.19</v>
+        <v>-0.75</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-101.12</t>
+          <t>-104.36</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1939682.155670103</t>
+          <t>1503043.582758621</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>1760233.0</t>
+          <t>1386639.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>1066636.2</v>
+        <v>1046928.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1150711.7</t>
+          <t>1156826.9</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>2566636.08</v>
+        <v>2577472.64</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-84075</t>
+          <t>-109898</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-260360.2422210338</t>
+          <t>-263833.401299818</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-324412.9035989079</t>
+          <t>-282935.7762331311</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>1760233.0</t>
+          <t>1386639.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,27 +6173,27 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>-8.972382204888667</t>
+          <t>0.8245111470917923</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>146.345773861391</t>
+          <t>135.4246787601293</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>132.2935565532715</t>
+          <t>132.6458021161182</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>81.24</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>28730</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6263,17 +6263,17 @@
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>317.0</t>
+          <t>307.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>317.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1510.0</t>
+          <t>5448.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>319.0</t>
+          <t>317.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6475,22 +6475,22 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2025-10-31 00:00:00</t>
+          <t>2025-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>135</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>53.57</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>51.19</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-1.15</v>
+        <v>-1.25</v>
       </c>
       <c r="AV13" t="n">
-        <v>-2.36</v>
+        <v>-2.27</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>322.7</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>330.5</v>
+        <v>328.45</v>
       </c>
       <c r="BA13" t="n">
-        <v>321.92</v>
+        <v>322.49</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>319.66</t>
+          <t>319.69</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-705.26</t>
+          <t>-953.47</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-1.62</v>
+        <v>-2.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.27</v>
+        <v>-0.19</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-98.45</t>
+          <t>-101.12</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1939682.155670103</t>
+          <t>1503043.582758621</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>481472.0</t>
+          <t>1760233.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>1054743.2</v>
+        <v>1066636.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1385012.3</t>
+          <t>1150711.7</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>2545738.9</v>
+        <v>2566636.08</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-330269</t>
+          <t>-84075</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-248714.3037886931</t>
+          <t>-260360.2422210338</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-412107.6961357708</t>
+          <t>-324412.9035989079</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>481472.0</t>
+          <t>1760233.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,42 +6660,42 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
         <is>
-          <t>-8.972382204888667</t>
+          <t>0.8245111470917923</t>
         </is>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>146.345773861391</t>
+          <t>135.4246787601293</t>
         </is>
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>132.2935565532715</t>
+          <t>132.6458021161182</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>81.24</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>28730</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>321.5</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>316.5</t>
+          <t>317.0</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>319.0</t>
+          <t>317.0</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2001.0</t>
+          <t>1510.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.28</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6962,22 +6962,22 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2025-10-31 00:00:00</t>
+          <t>2025-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>135</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>60.71</t>
+          <t>53.57</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.15</v>
       </c>
       <c r="AV14" t="n">
-        <v>-3.18</v>
+        <v>-2.36</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>322.6</t>
+          <t>322.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>333.2</v>
+        <v>330.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>321.29</v>
+        <v>321.92</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>319.52</t>
+          <t>319.66</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-271.33</t>
+          <t>-705.26</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-1.27</v>
+        <v>-1.62</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.74</v>
+        <v>0.27</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-95.71</t>
+          <t>-98.45</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1939682.155670103</t>
+          <t>1503043.582758621</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>641806.0</t>
+          <t>481472.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>1177470.8</v>
+        <v>1054743.2</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1764696.2</t>
+          <t>1385012.3</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>2550748.96</v>
+        <v>2545738.9</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-587225</t>
+          <t>-330269</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-219006.4142710426</t>
+          <t>-248714.3037886931</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-385657.7320407256</t>
+          <t>-412107.6961357708</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>641806.0</t>
+          <t>481472.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7147,27 +7147,27 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
         <is>
-          <t>-8.972382204888667</t>
+          <t>0.8245111470917923</t>
         </is>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>146.345773861391</t>
+          <t>135.4246787601293</t>
         </is>
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>132.2935565532715</t>
+          <t>132.6458021161182</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>81.24</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>28730</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>324.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>324.5</t>
+          <t>321.5</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>318.0</t>
+          <t>316.5</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2944.0</t>
+          <t>2001.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.86</t>
+          <t>-33.28</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7449,22 +7449,22 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2025-10-31 00:00:00</t>
+          <t>2025-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>135</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>45.77</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>0.62</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AV15" t="n">
-        <v>-4</v>
+        <v>-3.18</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>321.5</t>
+          <t>322.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>334.9</v>
+        <v>333.2</v>
       </c>
       <c r="BA15" t="n">
-        <v>320.76</v>
+        <v>321.29</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>319.49</t>
+          <t>319.52</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-172.52</t>
+          <t>-271.33</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.9</v>
+        <v>-1.27</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.24</v>
+        <v>0.74</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-92.79</t>
+          <t>-95.71</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1939682.155670103</t>
+          <t>1503043.582758621</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>964491.0</t>
+          <t>641806.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>1274696.2</v>
+        <v>1177470.8</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1927234.5</t>
+          <t>1764696.2</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>2556586.22</v>
+        <v>2550748.96</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-652538</t>
+          <t>-587225</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-188706.1746765548</t>
+          <t>-219006.4142710426</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-351277.2214749211</t>
+          <t>-385657.7320407256</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>964491.0</t>
+          <t>641806.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,27 +7634,27 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
         <is>
-          <t>-8.972382204888667</t>
+          <t>0.8245111470917923</t>
         </is>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>146.345773861391</t>
+          <t>135.4246787601293</t>
         </is>
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>132.2935565532715</t>
+          <t>132.6458021161182</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>81.24</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>28730</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>328.5</t>
+          <t>324.5</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>324.5</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4557.0</t>
+          <t>2944.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>325.5</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-39.16</t>
+          <t>-33.86</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7936,22 +7936,22 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2025-10-31 00:00:00</t>
+          <t>2025-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>135</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>2.01</v>
+        <v>0.62</v>
       </c>
       <c r="AV16" t="n">
-        <v>-4.87</v>
+        <v>-4</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>319.1</t>
+          <t>321.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>335.45</v>
+        <v>334.9</v>
       </c>
       <c r="BA16" t="n">
-        <v>320.26</v>
+        <v>320.76</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>319.48</t>
+          <t>319.49</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-143.66</t>
+          <t>-172.52</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.77</v>
+        <v>-0.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-89.68</t>
+          <t>-92.79</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1939682.155670103</t>
+          <t>1503043.582758621</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>1485179.0</t>
+          <t>964491.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>1266725.6</v>
+        <v>1274696.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>2082194.3</t>
+          <t>1927234.5</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>2560207.9</v>
+        <v>2556586.22</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-815468</t>
+          <t>-652538</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-159147.8025313973</t>
+          <t>-188706.1746765548</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-324189.9841853818</t>
+          <t>-351277.2214749211</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>1485179.0</t>
+          <t>964491.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,27 +8121,27 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
         <is>
-          <t>-8.972382204888667</t>
+          <t>0.8245111470917923</t>
         </is>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>146.345773861391</t>
+          <t>135.4246787601293</t>
         </is>
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>132.2935565532715</t>
+          <t>132.6458021161182</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>81.24</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>28730</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>329.5</t>
+          <t>328.5</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>331.5</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>325.5</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5199.0</t>
+          <t>4557.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-45.44</t>
+          <t>-39.16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8423,22 +8423,22 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2025-10-31 00:00:00</t>
+          <t>2025-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,12 +8449,12 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>135</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -8464,51 +8464,51 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>2.81</v>
+        <v>2.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>-5.48</v>
+        <v>-4.87</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>316.6</t>
+          <t>319.1</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>334.95</v>
+        <v>335.45</v>
       </c>
       <c r="BA17" t="n">
-        <v>319.43</v>
+        <v>320.26</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>319.18</t>
+          <t>319.48</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-133.52</t>
+          <t>-143.66</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.77</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.41</v>
+        <v>1.77</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-85.98</t>
+          <t>-89.68</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1939682.155670103</t>
+          <t>1503043.582758621</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>1700768.0</t>
+          <t>1485179.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>1234787.2</v>
+        <v>1266725.6</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>2263207.5</t>
+          <t>2082194.3</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>2579630.12</v>
+        <v>2560207.9</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-1028420</t>
+          <t>-815468</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-129140.1331397637</t>
+          <t>-159147.8025313973</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-329703.7171937048</t>
+          <t>-324189.9841853818</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>1700768.0</t>
+          <t>1485179.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8608,27 +8608,27 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
         <is>
-          <t>-8.972382204888667</t>
+          <t>0.8245111470917923</t>
         </is>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>146.345773861391</t>
+          <t>135.4246787601293</t>
         </is>
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>132.2935565532715</t>
+          <t>132.6458021161182</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>81.24</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>28730</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,17 +8693,17 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
+          <t>329.5</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>331.5</t>
+        </is>
+      </c>
+      <c r="CS17" t="inlineStr">
+        <is>
           <t>321.0</t>
-        </is>
-      </c>
-      <c r="CR17" t="inlineStr">
-        <is>
-          <t>331.0</t>
-        </is>
-      </c>
-      <c r="CS17" t="inlineStr">
-        <is>
-          <t>320.5</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3431.0</t>
+          <t>5199.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>318.5</t>
+          <t>325.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-28.75</t>
+          <t>-45.44</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8910,22 +8910,22 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2025-10-31 00:00:00</t>
+          <t>2025-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>135</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>1.21</v>
+        <v>2.81</v>
       </c>
       <c r="AV18" t="n">
-        <v>-5.91</v>
+        <v>-5.48</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>314.7</t>
+          <t>316.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>334.48</v>
+        <v>334.95</v>
       </c>
       <c r="BA18" t="n">
-        <v>319.08</v>
+        <v>319.43</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>318.9</t>
+          <t>319.18</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-126.10</t>
+          <t>-133.52</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.84</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.22</v>
+        <v>2.41</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-85.98</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1939682.155670103</t>
+          <t>1503043.582758621</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>1095110.0</t>
+          <t>1700768.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>1715281.4</v>
+        <v>1234787.2</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>2407407.4</t>
+          <t>2263207.5</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>2570986.38</v>
+        <v>2579630.12</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-692126</t>
+          <t>-1028420</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-92674.02694813808</t>
+          <t>-129140.1331397637</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-348904.1673058197</t>
+          <t>-329703.7171937048</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>1095110.0</t>
+          <t>1700768.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,27 +9095,27 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
         <is>
-          <t>-8.972382204888667</t>
+          <t>0.8245111470917923</t>
         </is>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>146.345773861391</t>
+          <t>135.4246787601293</t>
         </is>
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>132.2935565532715</t>
+          <t>132.6458021161182</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>81.24</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>28730</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>319.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>322.0</t>
+          <t>331.0</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>316.0</t>
+          <t>320.5</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>318.5</t>
+          <t>325.5</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3578.0</t>
+          <t>3431.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>314.5</t>
+          <t>318.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-28.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9397,22 +9397,22 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2025-10-31 00:00:00</t>
+          <t>2025-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>135</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AV19" t="n">
-        <v>-4.46</v>
+        <v>-5.91</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
+          <t>314.7</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>334.48</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>319.08</v>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
           <t>318.9</t>
         </is>
       </c>
-      <c r="AZ19" t="n">
-        <v>333.8</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>318.96</v>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>318.51</t>
-        </is>
-      </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-103.65</t>
+          <t>-126.10</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.15</v>
+        <v>-0.84</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.23</v>
+        <v>3.22</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-75.40</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1939682.155670103</t>
+          <t>1503043.582758621</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>1127933.0</t>
+          <t>1095110.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>2351921.6</v>
+        <v>1715281.4</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>2510974.0</t>
+          <t>2407407.4</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>2566859.44</v>
+        <v>2570986.38</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-159052</t>
+          <t>-692126</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-46086.72870128688</t>
+          <t>-92674.02694813808</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-298980.5900622043</t>
+          <t>-348904.1673058197</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>1127933.0</t>
+          <t>1095110.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,27 +9582,27 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
         <is>
-          <t>-8.972382204888667</t>
+          <t>0.8245111470917923</t>
         </is>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>146.345773861391</t>
+          <t>135.4246787601293</t>
         </is>
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>132.2935565532715</t>
+          <t>132.6458021161182</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>81.24</t>
+          <t>79.82</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>28730</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>315.5</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
+          <t>322.0</t>
+        </is>
+      </c>
+      <c r="CS19" t="inlineStr">
+        <is>
+          <t>316.0</t>
+        </is>
+      </c>
+      <c r="CT19" t="inlineStr">
+        <is>
           <t>318.5</t>
-        </is>
-      </c>
-      <c r="CS19" t="inlineStr">
-        <is>
-          <t>312.0</t>
-        </is>
-      </c>
-      <c r="CT19" t="inlineStr">
-        <is>
-          <t>314.5</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4357.0</t>
+          <t>3551.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-17.58</t>
+          <t>-29.14</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9884,22 +9884,22 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2024-11-08 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>77.89</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>87.15</t>
+          <t>79.78</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-3.26</v>
+        <v>-0.97</v>
       </c>
       <c r="AV20" t="n">
-        <v>19.98</v>
+        <v>17.42</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-4.70</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>60.06</t>
+          <t>59.77999999999999</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>50.06</v>
+        <v>50.91</v>
       </c>
       <c r="BA20" t="n">
-        <v>46.65</v>
+        <v>46.81</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>49.11</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-77.22</t>
+          <t>-75.47</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,48 +9988,48 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>1036225.722680412</t>
+          <t>717582.0165517242</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>253590.0</t>
+          <t>206305.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>429958.6</v>
+        <v>364889.4</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>521638.2</t>
+          <t>514959.5</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>165471.38</v>
+        <v>169166.64</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-91679</t>
+          <t>-150070</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>73719.65754160818</t>
+          <t>64024.66745592276</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>33936.79382193333</t>
+          <t>10702.22198465298</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>253590.0</t>
+          <t>206305.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10069,42 +10069,42 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
         <is>
-          <t>-13.11604617738421</t>
+          <t>7.123799359658484</t>
         </is>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>-89.8443596635741</t>
+          <t>-90.9911729201165</t>
         </is>
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>-89.26329698009079</t>
+          <t>-89.40880239801557</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>242.08</t>
+          <t>246.67</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10149,27 +10149,27 @@
       </c>
       <c r="CP20" t="inlineStr">
         <is>
-          <t>通信網路業右下上櫃</t>
+          <t>通信網路業平上櫃</t>
         </is>
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5615.0</t>
+          <t>4357.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,74 +10216,74 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-17.58</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2024-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2024-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>59.0</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2026-01-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2024-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2024-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>59.0</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>138.5</t>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10371,22 +10371,22 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2024-11-08 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>83.97</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>94.66</t>
+          <t>87.15</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-2.32</v>
+        <v>-3.26</v>
       </c>
       <c r="AV21" t="n">
-        <v>22.6</v>
+        <v>19.98</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.06</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>49.26</v>
+        <v>50.06</v>
       </c>
       <c r="BA21" t="n">
-        <v>46.51</v>
+        <v>46.65</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.11</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>56.70</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-79.44</t>
+          <t>-77.22</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,48 +10475,48 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>1036225.722680412</t>
+          <t>717582.0165517242</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>341670.0</t>
+          <t>253590.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>640798.4</v>
+        <v>429958.6</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>621223.7</t>
+          <t>521638.2</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>161045.58</v>
+        <v>165471.38</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>19574</t>
+          <t>-91679</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>80952.90549063997</t>
+          <t>73719.65754160818</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>60850.76095297909</t>
+          <t>33936.79382193333</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>341670.0</t>
+          <t>253590.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10556,42 +10556,42 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
         <is>
-          <t>-13.11604617738421</t>
+          <t>7.123799359658484</t>
         </is>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>-89.8443596635741</t>
+          <t>-90.9911729201165</t>
         </is>
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>-89.26329698009079</t>
+          <t>-89.40880239801557</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>242.08</t>
+          <t>246.67</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10636,27 +10636,27 @@
       </c>
       <c r="CP21" t="inlineStr">
         <is>
-          <t>通信網路業右下上櫃</t>
+          <t>通信網路業平上櫃</t>
         </is>
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5174.0</t>
+          <t>5615.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,27 +10713,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10858,22 +10858,22 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2024-11-08 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,50 +10884,50 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.97</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.66</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>2.2</v>
+        <v>-2.32</v>
       </c>
       <c r="AV22" t="n">
-        <v>23.89</v>
+        <v>22.6</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>48.42</v>
+        <v>49.26</v>
       </c>
       <c r="BA22" t="n">
-        <v>46.35</v>
+        <v>46.51</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
@@ -10936,14 +10936,14 @@
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>80.10</t>
+          <t>56.70</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>4.33</v>
+        <v>4.39</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-82.35</t>
+          <t>-79.44</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,48 +10962,48 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>1036225.722680412</t>
+          <t>717582.0165517242</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>317358.0</t>
+          <t>341670.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>762718.6</v>
+        <v>640798.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>611517.6</t>
+          <t>621223.7</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>155195.8</v>
+        <v>161045.58</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>151201</t>
+          <t>19574</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>84607.84086112375</t>
+          <t>80952.90549063997</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>87688.90110615233</t>
+          <t>60850.76095297909</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>317358.0</t>
+          <t>341670.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11043,42 +11043,42 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
         <is>
-          <t>-13.11604617738421</t>
+          <t>7.123799359658484</t>
         </is>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>-89.8443596635741</t>
+          <t>-90.9911729201165</t>
         </is>
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>-89.26329698009079</t>
+          <t>-89.40880239801557</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>242.08</t>
+          <t>246.67</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11123,27 +11123,27 @@
       </c>
       <c r="CP22" t="inlineStr">
         <is>
-          <t>通信網路業右下上櫃</t>
+          <t>通信網路業平上櫃</t>
         </is>
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11279.0</t>
+          <t>5174.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30.30</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11345,38 +11345,38 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2024-11-08 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11390,47 +11390,47 @@
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>5.54</v>
+        <v>2.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>22.31</v>
+        <v>23.89</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>47.48</v>
+        <v>48.42</v>
       </c>
       <c r="BA23" t="n">
-        <v>46.11</v>
+        <v>46.35</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>105.80</t>
+          <t>80.10</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>3.96</v>
+        <v>4.33</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-85.89</t>
+          <t>-82.35</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>1036225.722680412</t>
+          <t>717582.0165517242</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>705524.0</t>
+          <t>317358.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>770207.6</v>
+        <v>762718.6</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>591103.1</t>
+          <t>611517.6</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>149283.02</v>
+        <v>155195.8</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>179104</t>
+          <t>151201</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>84047.64808930038</t>
+          <t>84607.84086112375</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>125502.2119997515</t>
+          <t>87688.90110615233</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>705524.0</t>
+          <t>317358.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11530,27 +11530,27 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
         <is>
-          <t>-13.11604617738421</t>
+          <t>7.123799359658484</t>
         </is>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>-89.8443596635741</t>
+          <t>-90.9911729201165</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>-89.26329698009079</t>
+          <t>-89.40880239801557</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>242.08</t>
+          <t>246.67</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11610,22 +11610,22 @@
       </c>
       <c r="CP23" t="inlineStr">
         <is>
-          <t>通信網路業右下上櫃</t>
+          <t>通信網路業平上櫃</t>
         </is>
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8858.0</t>
+          <t>11279.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>30.30</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11832,22 +11832,22 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2024-11-08 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11877,47 +11877,47 @@
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>9.699999999999999</v>
+        <v>5.54</v>
       </c>
       <c r="AV24" t="n">
-        <v>18.59</v>
+        <v>22.31</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>55.23999999999999</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>46.58</v>
+        <v>47.48</v>
       </c>
       <c r="BA24" t="n">
-        <v>45.89</v>
+        <v>46.11</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>142.06</t>
+          <t>105.80</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>3.42</v>
+        <v>3.96</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-89.62</t>
+          <t>-85.89</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1036225.722680412</t>
+          <t>717582.0165517242</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>531651.0</t>
+          <t>705524.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>665029.6</v>
+        <v>770207.6</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>523057.5</t>
+          <t>591103.1</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>135986.22</v>
+        <v>149283.02</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>141972</t>
+          <t>179104</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>76510.45465103655</t>
+          <t>84047.64808930038</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>133449.7914191877</t>
+          <t>125502.2119997515</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>531651.0</t>
+          <t>705524.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12017,42 +12017,42 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
         <is>
-          <t>-13.11604617738421</t>
+          <t>7.123799359658484</t>
         </is>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>-89.8443596635741</t>
+          <t>-90.9911729201165</t>
         </is>
       </c>
       <c r="CC24" t="inlineStr">
         <is>
-          <t>-89.26329698009079</t>
+          <t>-89.40880239801557</t>
         </is>
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>242.08</t>
+          <t>246.67</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12097,27 +12097,27 @@
       </c>
       <c r="CP24" t="inlineStr">
         <is>
-          <t>通信網路業右下上櫃</t>
+          <t>通信網路業平上櫃</t>
         </is>
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
+          <t>65.1</t>
+        </is>
+      </c>
+      <c r="CS24" t="inlineStr">
+        <is>
+          <t>58.6</t>
+        </is>
+      </c>
+      <c r="CT24" t="inlineStr">
+        <is>
           <t>61.3</t>
-        </is>
-      </c>
-      <c r="CS24" t="inlineStr">
-        <is>
-          <t>58.4</t>
-        </is>
-      </c>
-      <c r="CT24" t="inlineStr">
-        <is>
-          <t>60.6</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21925.0</t>
+          <t>8858.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>27.14</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12319,22 +12319,22 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2024-11-08 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>53.61</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12364,47 +12364,47 @@
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>13.88</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AV25" t="n">
-        <v>14.94</v>
+        <v>18.59</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-7.00</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>52.51000000000001</t>
+          <t>55.23999999999999</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>45.68</v>
+        <v>46.58</v>
       </c>
       <c r="BA25" t="n">
-        <v>45.66</v>
+        <v>45.89</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>203.00</t>
+          <t>142.06</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>2.76</v>
+        <v>3.42</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.91</v>
+        <v>1.41</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-93.31</t>
+          <t>-89.62</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1036225.722680412</t>
+          <t>717582.0165517242</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>1307789.0</t>
+          <t>531651.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>613317.8</v>
+        <v>665029.6</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>472603.9</t>
+          <t>523057.5</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>125932.14</v>
+        <v>135986.22</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>140713</t>
+          <t>141972</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>66157.84796591816</t>
+          <t>76510.45465103655</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>158666.66232484</t>
+          <t>133449.7914191877</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>1307789.0</t>
+          <t>531651.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12504,42 +12504,42 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
         <is>
-          <t>-13.11604617738421</t>
+          <t>7.123799359658484</t>
         </is>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>-89.8443596635741</t>
+          <t>-90.9911729201165</t>
         </is>
       </c>
       <c r="CC25" t="inlineStr">
         <is>
-          <t>-89.26329698009079</t>
+          <t>-89.40880239801557</t>
         </is>
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>242.08</t>
+          <t>246.67</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12584,27 +12584,27 @@
       </c>
       <c r="CP25" t="inlineStr">
         <is>
-          <t>通信網路業右下上櫃</t>
+          <t>通信網路業平上櫃</t>
         </is>
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12626,7 +12626,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>17344.0</t>
+          <t>21925.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>74.90</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12806,38 +12806,38 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2024-11-08 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>53.61</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12847,51 +12847,51 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>88.55</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>12.34</v>
+        <v>13.88</v>
       </c>
       <c r="AV26" t="n">
-        <v>13.02</v>
+        <v>14.94</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.00</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>52.51000000000001</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>44.82</v>
+        <v>45.68</v>
       </c>
       <c r="BA26" t="n">
-        <v>45.45</v>
+        <v>45.66</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>49.11</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>336.90</t>
+          <t>203.00</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>1.96</v>
+        <v>2.76</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-96.70</t>
+          <t>-93.31</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1036225.722680412</t>
+          <t>717582.0165517242</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>951271.0</t>
+          <t>1307789.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>601649</v>
+        <v>613317.8</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>343989.9</t>
+          <t>472603.9</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>100400.3</v>
+        <v>125932.14</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>257659</t>
+          <t>140713</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>49338.06353702328</t>
+          <t>66157.84796591816</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>105866.4542498846</t>
+          <t>158666.66232484</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>951271.0</t>
+          <t>1307789.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,27 +12991,27 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
         <is>
-          <t>-13.11604617738421</t>
+          <t>7.123799359658484</t>
         </is>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>-89.8443596635741</t>
+          <t>-90.9911729201165</t>
         </is>
       </c>
       <c r="CC26" t="inlineStr">
         <is>
-          <t>-89.26329698009079</t>
+          <t>-89.40880239801557</t>
         </is>
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>242.08</t>
+          <t>246.67</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13071,27 +13071,27 @@
       </c>
       <c r="CP26" t="inlineStr">
         <is>
-          <t>通信網路業右下上櫃</t>
+          <t>通信網路業平上櫃</t>
         </is>
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7063.0</t>
+          <t>17344.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>82.91</t>
+          <t>74.90</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13293,22 +13293,22 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2024-11-08 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>17.27</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13334,51 +13334,51 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>88.55</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>5.13</v>
+        <v>12.34</v>
       </c>
       <c r="AV27" t="n">
-        <v>11.96</v>
+        <v>13.02</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-7.86</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>50.65</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>44.01</v>
+        <v>44.82</v>
       </c>
       <c r="BA27" t="n">
-        <v>45.31</v>
+        <v>45.45</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>49.18</t>
+          <t>49.11</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>1603.09</t>
+          <t>336.90</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>1.21</v>
+        <v>1.96</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-99.48</t>
+          <t>-96.70</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1036225.722680412</t>
+          <t>717582.0165517242</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>354803.0</t>
+          <t>951271.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>460316.6</v>
+        <v>601649</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>251659.1</t>
+          <t>343989.9</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>82011.2</v>
+        <v>100400.3</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>208657</t>
+          <t>257659</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>39060.17431650303</t>
+          <t>49338.06353702328</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>64854.99791959545</t>
+          <t>105866.4542498846</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>354803.0</t>
+          <t>951271.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,27 +13478,27 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
         <is>
-          <t>-13.11604617738421</t>
+          <t>7.123799359658484</t>
         </is>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>-89.8443596635741</t>
+          <t>-90.9911729201165</t>
         </is>
       </c>
       <c r="CC27" t="inlineStr">
         <is>
-          <t>-89.26329698009079</t>
+          <t>-89.40880239801557</t>
         </is>
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>242.08</t>
+          <t>246.67</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13558,27 +13558,27 @@
       </c>
       <c r="CP27" t="inlineStr">
         <is>
-          <t>通信網路業右下上櫃</t>
+          <t>通信網路業平上櫃</t>
         </is>
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3819.0</t>
+          <t>7063.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>88.28</t>
+          <t>82.91</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13780,22 +13780,22 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2024-11-08 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>17.27</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,17 +13806,17 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>65.66</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
@@ -13825,47 +13825,47 @@
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-1.9</v>
+        <v>5.13</v>
       </c>
       <c r="AV28" t="n">
-        <v>10.54</v>
+        <v>11.96</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-8.15</t>
+          <t>-7.86</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>48.01000000000001</t>
+          <t>49.27</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>43.43</v>
+        <v>44.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>45.28</v>
+        <v>45.31</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.18</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>449.01</t>
+          <t>1603.09</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.74</v>
+        <v>1.21</v>
       </c>
       <c r="BE28" t="n">
-        <v>-0.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-101.56</t>
+          <t>-99.48</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1036225.722680412</t>
+          <t>717582.0165517242</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>179634.0</t>
+          <t>354803.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>411998.6</v>
+        <v>460316.6</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>218827.9</t>
+          <t>251659.1</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>75776.96000000001</v>
+        <v>82011.2</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>193170</t>
+          <t>208657</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>34370.20638866805</t>
+          <t>39060.17431650303</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>67858.23895062532</t>
+          <t>64854.99791959545</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>179634.0</t>
+          <t>354803.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-21.24</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,27 +13965,27 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
         <is>
-          <t>-13.11604617738421</t>
+          <t>7.123799359658484</t>
         </is>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>-89.8443596635741</t>
+          <t>-90.9911729201165</t>
         </is>
       </c>
       <c r="CC28" t="inlineStr">
         <is>
-          <t>-89.26329698009079</t>
+          <t>-89.40880239801557</t>
         </is>
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>242.08</t>
+          <t>246.67</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>282.69</t>
+          <t>276.56</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14045,27 +14045,27 @@
       </c>
       <c r="CP28" t="inlineStr">
         <is>
-          <t>通信網路業右下上櫃</t>
+          <t>通信網路業平上櫃</t>
         </is>
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/印刷電路板.xlsx
+++ b/Result/checksun_type/印刷電路板.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,61 +1149,61 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>67.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.45</v>
+        <v>2.42</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.88</v>
+        <v>-1.37</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>42.74</v>
+        <v>42.72</v>
       </c>
       <c r="BA2" t="n">
-        <v>42.58</v>
+        <v>42.64</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>41.93</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-109.73</t>
+          <t>-27.73</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.24</v>
+        <v>-0.16</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-102.77</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>76619.90689655172</t>
+          <t>76527.58884297521</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>7093.0</t>
+          <t>6398.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>4432.8</v>
+        <v>5052.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>3641.8</t>
+          <t>4126.7</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>5324.22</v>
+        <v>5396.04</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>925</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-159.2021487908879</t>
+          <t>-65.79690900617473</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>324.5656328396403</t>
+          <t>447.9319098097476</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>7093.0</t>
+          <t>6398.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,45 +1636,45 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>67.86</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.41</v>
+        <v>1.45</v>
       </c>
       <c r="AV3" t="n">
-        <v>-2.21</v>
+        <v>-1.88</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>42.82</v>
+        <v>42.74</v>
       </c>
       <c r="BA3" t="n">
-        <v>42.55</v>
+        <v>42.58</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-237.95</t>
+          <t>-109.73</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.28</v>
+        <v>-0.24</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-101.87</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>76619.90689655172</t>
+          <t>76527.58884297521</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>4588.0</t>
+          <t>7093.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>4106.8</v>
+        <v>4432.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>3135.4</t>
+          <t>3641.8</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>5210.02</v>
+        <v>5324.22</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>791</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-247.1599272691658</t>
+          <t>-159.2021487908879</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>62.27217885235677</t>
+          <t>324.5656328396403</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>4588.0</t>
+          <t>7093.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,92 +2022,92 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-18.18</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>46.1</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/04/11</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>43.8</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>42.05</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2024-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>7.59</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
           <t>-0.60</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-18.18</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>46.1</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/04/11</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>42.05</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>3.93</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>-0.36</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,45 +2123,45 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
           <t>3.57</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
       <c r="AU4" t="n">
-        <v>-0.88</v>
+        <v>-0.41</v>
       </c>
       <c r="AV4" t="n">
-        <v>-2.02</v>
+        <v>-2.21</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>42.89</v>
+        <v>42.82</v>
       </c>
       <c r="BA4" t="n">
-        <v>42.53</v>
+        <v>42.55</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-616.22</t>
+          <t>-237.95</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-100.76</t>
+          <t>-101.87</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>76619.90689655172</t>
+          <t>76527.58884297521</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>2390.0</t>
+          <t>4588.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>3455.4</v>
+        <v>4106.8</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>2936.2</t>
+          <t>3135.4</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>5165.48</v>
+        <v>5210.02</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>971</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-303.4203102003517</t>
+          <t>-247.1599272691658</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-46.26390465991744</t>
+          <t>62.27217885235677</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>2390.0</t>
+          <t>4588.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
+          <t>41.65</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>42.05</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
           <t>41.6</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>41.85</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
-      </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,45 +2610,45 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.42</v>
+        <v>-0.88</v>
       </c>
       <c r="AV5" t="n">
-        <v>-1.77</v>
+        <v>-2.02</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>42.96</v>
+        <v>42.89</v>
       </c>
       <c r="BA5" t="n">
-        <v>42.52</v>
+        <v>42.53</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1098.80</t>
+          <t>-616.22</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.18</v>
+        <v>-0.24</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-99.59</t>
+          <t>-100.76</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>76619.90689655172</t>
+          <t>76527.58884297521</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>4794.0</t>
+          <t>2390.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>3682</v>
+        <v>3455.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>2940.4</t>
+          <t>2936.2</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>5156.86</v>
+        <v>5165.48</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>519</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-350.1760202986125</t>
+          <t>-303.4203102003517</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>35.83682977468789</t>
+          <t>-46.26390465991744</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>4794.0</t>
+          <t>2390.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,42 +2896,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>-1.43</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>41.6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>42.2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3111,47 +3111,47 @@
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.66</v>
+        <v>-1.42</v>
       </c>
       <c r="AV6" t="n">
-        <v>-1.33</v>
+        <v>-1.77</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>43.05</v>
+        <v>42.96</v>
       </c>
       <c r="BA6" t="n">
-        <v>42.5</v>
+        <v>42.52</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-244.02</t>
+          <t>-1098.80</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.1</v>
+        <v>-0.18</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-98.47</t>
+          <t>-99.59</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>76619.90689655172</t>
+          <t>76527.58884297521</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>3299.0</t>
+          <t>4794.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>3200.8</v>
+        <v>3682</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>2720.2</t>
+          <t>2940.4</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>5152.92</v>
+        <v>5156.86</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>741</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-420.3601748573943</t>
+          <t>-350.1760202986125</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-105.7277220964011</t>
+          <t>35.83682977468789</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>3299.0</t>
+          <t>4794.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>17.67</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3598,31 +3598,31 @@
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.99</v>
+        <v>-0.66</v>
       </c>
       <c r="AV7" t="n">
-        <v>-1.24</v>
+        <v>-1.33</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>42.48</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>43.15</v>
+        <v>43.05</v>
       </c>
       <c r="BA7" t="n">
-        <v>42.47</v>
+        <v>42.5</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-147.29</t>
+          <t>-244.02</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-97.53</t>
+          <t>-98.47</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>76619.90689655172</t>
+          <t>76527.58884297521</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>5463.0</t>
+          <t>3299.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>2850.8</v>
+        <v>3200.8</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>2592.2</t>
+          <t>2720.2</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>5117.16</v>
+        <v>5152.92</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>480</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-477.5660753593931</t>
+          <t>-420.3601748573943</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-144.0082346945132</t>
+          <t>-105.7277220964011</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>5463.0</t>
+          <t>3299.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4081,51 +4081,51 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.7</v>
+        <v>-0.99</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.01</v>
+        <v>-1.24</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>43.19</v>
+        <v>43.15</v>
       </c>
       <c r="BA8" t="n">
-        <v>42.42</v>
+        <v>42.47</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-94.73</t>
+          <t>-147.29</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-96.62</t>
+          <t>-97.53</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>76619.90689655172</t>
+          <t>76527.58884297521</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>1331.0</t>
+          <t>5463.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>2164</v>
+        <v>2850.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>2415.9</t>
+          <t>2592.2</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>5055.46</v>
+        <v>5117.16</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-251</t>
+          <t>258</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-538.2129554802804</t>
+          <t>-477.5660753593931</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-425.4086728812981</t>
+          <t>-144.0082346945132</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>1331.0</t>
+          <t>5463.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-9.22</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4568,35 +4568,35 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.82</v>
+        <v>-0.7</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.68</v>
+        <v>-1.01</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>43.2</v>
+        <v>43.19</v>
       </c>
       <c r="BA9" t="n">
-        <v>42.37</v>
+        <v>42.42</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-68.56</t>
+          <t>-94.73</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-95.82</t>
+          <t>-96.62</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>76619.90689655172</t>
+          <t>76527.58884297521</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>3523.0</t>
+          <t>1331.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>2417</v>
+        <v>2164</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>2662.5</t>
+          <t>2415.9</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>5123.08</v>
+        <v>5055.46</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-245</t>
+          <t>-251</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-558.7228250437316</t>
+          <t>-538.2129554802804</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-369.5018462595149</t>
+          <t>-425.4086728812981</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>3523.0</t>
+          <t>1331.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.94</t>
+          <t>-9.22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,163 +5045,163 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.02</v>
+        <v>-0.82</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.38</v>
+        <v>-0.68</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>41.91</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-68.56</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-95.82</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>76527.58884297521</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>3523.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="n">
+        <v>2417</v>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>2662.5</t>
+        </is>
+      </c>
+      <c r="BM10" t="n">
+        <v>5123.08</v>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-245</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-558.7228250437316</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-369.5018462595149</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>3523.0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>宇智</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>宇智</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>43.01000000000001</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>43.17</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>42.32</v>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>41.91</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-48.66</t>
-        </is>
-      </c>
-      <c r="BD10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>4.39</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-95.10</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>76619.90689655172</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>2388.0</t>
-        </is>
-      </c>
-      <c r="BK10" t="n">
-        <v>2198.8</v>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>2585.0</t>
-        </is>
-      </c>
-      <c r="BM10" t="n">
-        <v>5187.66</v>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-386</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-593.1266393681346</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>-511.2955994334138</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>2388.0</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>宇智</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>宇智</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
       <c r="CA10" t="inlineStr">
         <is>
           <t>-2.035038170073544</t>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3223.0</t>
+          <t>5367.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>305.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>78.05</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-2.87</v>
+        <v>2.16</v>
       </c>
       <c r="AV11" t="n">
-        <v>-3.61</v>
+        <v>-3.29</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>314.0</t>
+          <t>314.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>325.75</v>
+        <v>324.88</v>
       </c>
       <c r="BA11" t="n">
-        <v>323.37</v>
+        <v>324.08</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>318.96</t>
+          <t>318.91</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-185.73</t>
+          <t>-91.62</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-4</v>
+        <v>-3.48</v>
       </c>
       <c r="BE11" t="n">
-        <v>-1.4</v>
+        <v>-1.82</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-108.14</t>
+          <t>-110.56</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>1503043.582758621</t>
+          <t>1504487.785123967</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>986882.0</t>
+          <t>1701023.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>1051406.4</v>
+        <v>1263249.8</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1163051.3</t>
+          <t>1220360.3</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>2582295.04</v>
+        <v>2598674.62</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-111644</t>
+          <t>42889</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-265829.8268954243</t>
+          <t>-257554.686217077</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-276810.167671259</t>
+          <t>-212041.4124861672</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>986882.0</t>
+          <t>1701023.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>29845</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>311.0</t>
+          <t>305.5</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>314.5</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>299.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>305.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4451.0</t>
+          <t>3223.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,12 +6014,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6029,51 +6029,51 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-2.74</v>
+        <v>-2.87</v>
       </c>
       <c r="AV12" t="n">
-        <v>-2.88</v>
+        <v>-3.61</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>317.7</t>
+          <t>314.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>327.12</v>
+        <v>325.75</v>
       </c>
       <c r="BA12" t="n">
-        <v>322.85</v>
+        <v>323.37</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>319.5</t>
+          <t>318.96</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-296.96</t>
+          <t>-185.73</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-2.98</v>
+        <v>-4</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.75</v>
+        <v>-1.4</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-104.36</t>
+          <t>-108.14</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1503043.582758621</t>
+          <t>1504487.785123967</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>1386639.0</t>
+          <t>986882.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>1046928.2</v>
+        <v>1051406.4</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1156826.9</t>
+          <t>1163051.3</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>2577472.64</v>
+        <v>2582295.04</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-109898</t>
+          <t>-111644</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-263833.401299818</t>
+          <t>-265829.8268954243</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-282935.7762331311</t>
+          <t>-276810.167671259</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>1386639.0</t>
+          <t>986882.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>29845</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>319.0</t>
+          <t>311.0</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>314.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>307.5</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5448.0</t>
+          <t>4451.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>317.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>51.19</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-1.25</v>
+        <v>-2.74</v>
       </c>
       <c r="AV13" t="n">
-        <v>-2.27</v>
+        <v>-2.88</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>317.7</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>328.45</v>
+        <v>327.12</v>
       </c>
       <c r="BA13" t="n">
-        <v>322.49</v>
+        <v>322.85</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>319.69</t>
+          <t>319.5</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-953.47</t>
+          <t>-296.96</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-2.03</v>
+        <v>-2.98</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.19</v>
+        <v>-0.75</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-101.12</t>
+          <t>-104.36</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1503043.582758621</t>
+          <t>1504487.785123967</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>1760233.0</t>
+          <t>1386639.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>1066636.2</v>
+        <v>1046928.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1150711.7</t>
+          <t>1156826.9</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>2566636.08</v>
+        <v>2577472.64</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-84075</t>
+          <t>-109898</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-260360.2422210338</t>
+          <t>-263833.401299818</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-324412.9035989079</t>
+          <t>-282935.7762331311</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>1760233.0</t>
+          <t>1386639.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>29845</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6750,17 +6750,17 @@
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>317.0</t>
+          <t>307.5</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>317.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1510.0</t>
+          <t>5448.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>319.0</t>
+          <t>317.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>53.57</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>51.19</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-1.15</v>
+        <v>-1.25</v>
       </c>
       <c r="AV14" t="n">
-        <v>-2.36</v>
+        <v>-2.27</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>322.7</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>330.5</v>
+        <v>328.45</v>
       </c>
       <c r="BA14" t="n">
-        <v>321.92</v>
+        <v>322.49</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>319.66</t>
+          <t>319.69</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-705.26</t>
+          <t>-953.47</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-1.62</v>
+        <v>-2.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.27</v>
+        <v>-0.19</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-98.45</t>
+          <t>-101.12</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1503043.582758621</t>
+          <t>1504487.785123967</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>481472.0</t>
+          <t>1760233.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>1054743.2</v>
+        <v>1066636.2</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1385012.3</t>
+          <t>1150711.7</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>2545738.9</v>
+        <v>2566636.08</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-330269</t>
+          <t>-84075</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-248714.3037886931</t>
+          <t>-260360.2422210338</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-412107.6961357708</t>
+          <t>-324412.9035989079</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>481472.0</t>
+          <t>1760233.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>29845</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>321.5</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>316.5</t>
+          <t>317.0</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>319.0</t>
+          <t>317.0</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2001.0</t>
+          <t>1510.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.28</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>60.71</t>
+          <t>53.57</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.15</v>
       </c>
       <c r="AV15" t="n">
-        <v>-3.18</v>
+        <v>-2.36</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>322.6</t>
+          <t>322.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>333.2</v>
+        <v>330.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>321.29</v>
+        <v>321.92</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>319.52</t>
+          <t>319.66</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-271.33</t>
+          <t>-705.26</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-1.27</v>
+        <v>-1.62</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.74</v>
+        <v>0.27</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-95.71</t>
+          <t>-98.45</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1503043.582758621</t>
+          <t>1504487.785123967</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>641806.0</t>
+          <t>481472.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>1177470.8</v>
+        <v>1054743.2</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1764696.2</t>
+          <t>1385012.3</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>2550748.96</v>
+        <v>2545738.9</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-587225</t>
+          <t>-330269</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-219006.4142710426</t>
+          <t>-248714.3037886931</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-385657.7320407256</t>
+          <t>-412107.6961357708</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>641806.0</t>
+          <t>481472.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>29845</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>324.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>324.5</t>
+          <t>321.5</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>318.0</t>
+          <t>316.5</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2944.0</t>
+          <t>2001.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.86</t>
+          <t>-33.28</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>45.77</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>0.62</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>-4</v>
+        <v>-3.18</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>321.5</t>
+          <t>322.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>334.9</v>
+        <v>333.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>320.76</v>
+        <v>321.29</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>319.49</t>
+          <t>319.52</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-172.52</t>
+          <t>-271.33</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.9</v>
+        <v>-1.27</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.24</v>
+        <v>0.74</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-92.79</t>
+          <t>-95.71</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1503043.582758621</t>
+          <t>1504487.785123967</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>964491.0</t>
+          <t>641806.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>1274696.2</v>
+        <v>1177470.8</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1927234.5</t>
+          <t>1764696.2</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>2556586.22</v>
+        <v>2550748.96</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-652538</t>
+          <t>-587225</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-188706.1746765548</t>
+          <t>-219006.4142710426</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-351277.2214749211</t>
+          <t>-385657.7320407256</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>964491.0</t>
+          <t>641806.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>29845</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>328.5</t>
+          <t>324.5</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>324.5</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4557.0</t>
+          <t>2944.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>325.5</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-39.16</t>
+          <t>-33.86</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>2.01</v>
+        <v>0.62</v>
       </c>
       <c r="AV17" t="n">
-        <v>-4.87</v>
+        <v>-4</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>319.1</t>
+          <t>321.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>335.45</v>
+        <v>334.9</v>
       </c>
       <c r="BA17" t="n">
-        <v>320.26</v>
+        <v>320.76</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>319.48</t>
+          <t>319.49</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-143.66</t>
+          <t>-172.52</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.77</v>
+        <v>-0.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-89.68</t>
+          <t>-92.79</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1503043.582758621</t>
+          <t>1504487.785123967</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>1485179.0</t>
+          <t>964491.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>1266725.6</v>
+        <v>1274696.2</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>2082194.3</t>
+          <t>1927234.5</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>2560207.9</v>
+        <v>2556586.22</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-815468</t>
+          <t>-652538</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-159147.8025313973</t>
+          <t>-188706.1746765548</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-324189.9841853818</t>
+          <t>-351277.2214749211</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>1485179.0</t>
+          <t>964491.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8628,22 +8628,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>29845</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>329.5</t>
+          <t>328.5</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>331.5</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>325.5</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5199.0</t>
+          <t>4557.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-45.44</t>
+          <t>-39.16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,12 +8936,12 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8951,51 +8951,51 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>2.81</v>
+        <v>2.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>-5.48</v>
+        <v>-4.87</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>316.6</t>
+          <t>319.1</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>334.95</v>
+        <v>335.45</v>
       </c>
       <c r="BA18" t="n">
-        <v>319.43</v>
+        <v>320.26</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>319.18</t>
+          <t>319.48</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-133.52</t>
+          <t>-143.66</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.77</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.41</v>
+        <v>1.77</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-85.98</t>
+          <t>-89.68</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1503043.582758621</t>
+          <t>1504487.785123967</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>1700768.0</t>
+          <t>1485179.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>1234787.2</v>
+        <v>1266725.6</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>2263207.5</t>
+          <t>2082194.3</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>2579630.12</v>
+        <v>2560207.9</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-1028420</t>
+          <t>-815468</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-129140.1331397637</t>
+          <t>-159147.8025313973</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-329703.7171937048</t>
+          <t>-324189.9841853818</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>1700768.0</t>
+          <t>1485179.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>29845</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,17 +9180,17 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
+          <t>329.5</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>331.5</t>
+        </is>
+      </c>
+      <c r="CS18" t="inlineStr">
+        <is>
           <t>321.0</t>
-        </is>
-      </c>
-      <c r="CR18" t="inlineStr">
-        <is>
-          <t>331.0</t>
-        </is>
-      </c>
-      <c r="CS18" t="inlineStr">
-        <is>
-          <t>320.5</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3431.0</t>
+          <t>5199.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>318.5</t>
+          <t>325.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-28.75</t>
+          <t>-45.44</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>1.21</v>
+        <v>2.81</v>
       </c>
       <c r="AV19" t="n">
-        <v>-5.91</v>
+        <v>-5.48</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>314.7</t>
+          <t>316.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>334.48</v>
+        <v>334.95</v>
       </c>
       <c r="BA19" t="n">
-        <v>319.08</v>
+        <v>319.43</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>318.9</t>
+          <t>319.18</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-126.10</t>
+          <t>-133.52</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.84</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.22</v>
+        <v>2.41</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-85.98</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1503043.582758621</t>
+          <t>1504487.785123967</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>1095110.0</t>
+          <t>1700768.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>1715281.4</v>
+        <v>1234787.2</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>2407407.4</t>
+          <t>2263207.5</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>2570986.38</v>
+        <v>2579630.12</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-692126</t>
+          <t>-1028420</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-92674.02694813808</t>
+          <t>-129140.1331397637</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-348904.1673058197</t>
+          <t>-329703.7171937048</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>1095110.0</t>
+          <t>1700768.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>29845</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>319.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>322.0</t>
+          <t>331.0</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>316.0</t>
+          <t>320.5</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>318.5</t>
+          <t>325.5</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9704,7 +9704,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3551.0</t>
+          <t>5573.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-29.14</t>
+          <t>-45.14</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>77.89</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>79.78</t>
+          <t>71.48</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.97</v>
+        <v>0.13</v>
       </c>
       <c r="AV20" t="n">
-        <v>17.42</v>
+        <v>14.71</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-4.70</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>59.77999999999999</t>
+          <t>59.41999999999999</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>50.91</v>
+        <v>51.8</v>
       </c>
       <c r="BA20" t="n">
-        <v>46.81</v>
+        <v>47.01</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.13</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-75.47</t>
+          <t>-74.13</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,48 +9988,48 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>717582.0165517242</t>
+          <t>717289.3285123967</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>206305.0</t>
+          <t>336727.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>364889.4</v>
+        <v>291130</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>514959.5</t>
+          <t>530668.8</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>169166.64</v>
+        <v>174983.32</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-150070</t>
+          <t>-239538</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>64024.66745592276</t>
+          <t>54782.7364856178</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>10702.22198465298</t>
+          <t>3952.116148940462</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>206305.0</t>
+          <t>336727.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,22 +10089,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>246.67</t>
+          <t>247.92</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>62.7</t>
+        </is>
+      </c>
+      <c r="CS20" t="inlineStr">
+        <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="CR20" t="inlineStr">
+      <c r="CT20" t="inlineStr">
         <is>
           <t>59.5</t>
-        </is>
-      </c>
-      <c r="CS20" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="CT20" t="inlineStr">
-        <is>
-          <t>59.2</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4357.0</t>
+          <t>3551.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-17.58</t>
+          <t>-29.14</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>77.89</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>87.15</t>
+          <t>79.78</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-3.26</v>
+        <v>-0.97</v>
       </c>
       <c r="AV21" t="n">
-        <v>19.98</v>
+        <v>17.42</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-4.70</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>60.06</t>
+          <t>59.77999999999999</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>50.06</v>
+        <v>50.91</v>
       </c>
       <c r="BA21" t="n">
-        <v>46.65</v>
+        <v>46.81</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>49.11</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="BE21" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-77.22</t>
+          <t>-75.47</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,48 +10475,48 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>717582.0165517242</t>
+          <t>717289.3285123967</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>253590.0</t>
+          <t>206305.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>429958.6</v>
+        <v>364889.4</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>521638.2</t>
+          <t>514959.5</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>165471.38</v>
+        <v>169166.64</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-91679</t>
+          <t>-150070</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>73719.65754160818</t>
+          <t>64024.66745592276</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>33936.79382193333</t>
+          <t>10702.22198465298</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>253590.0</t>
+          <t>206305.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,22 +10576,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>246.67</t>
+          <t>247.92</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5615.0</t>
+          <t>4357.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,74 +10703,74 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-17.58</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2024-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2024-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>59.0</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2024-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2024-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>59.0</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>138.5</t>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>83.97</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>94.66</t>
+          <t>87.15</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-2.32</v>
+        <v>-3.26</v>
       </c>
       <c r="AV22" t="n">
-        <v>22.6</v>
+        <v>19.98</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.06</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>49.26</v>
+        <v>50.06</v>
       </c>
       <c r="BA22" t="n">
-        <v>46.51</v>
+        <v>46.65</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.11</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>56.70</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-79.44</t>
+          <t>-77.22</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,48 +10962,48 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>717582.0165517242</t>
+          <t>717289.3285123967</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>341670.0</t>
+          <t>253590.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>640798.4</v>
+        <v>429958.6</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>621223.7</t>
+          <t>521638.2</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>161045.58</v>
+        <v>165471.38</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>19574</t>
+          <t>-91679</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>80952.90549063997</t>
+          <t>73719.65754160818</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>60850.76095297909</t>
+          <t>33936.79382193333</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>341670.0</t>
+          <t>253590.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,22 +11063,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>246.67</t>
+          <t>247.92</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5174.0</t>
+          <t>5615.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,22 +11200,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,50 +11371,50 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.97</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.66</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>2.2</v>
+        <v>-2.32</v>
       </c>
       <c r="AV23" t="n">
-        <v>23.89</v>
+        <v>22.6</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>48.42</v>
+        <v>49.26</v>
       </c>
       <c r="BA23" t="n">
-        <v>46.35</v>
+        <v>46.51</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
@@ -11423,14 +11423,14 @@
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>80.10</t>
+          <t>56.70</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>4.33</v>
+        <v>4.39</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-82.35</t>
+          <t>-79.44</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,48 +11449,48 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>717582.0165517242</t>
+          <t>717289.3285123967</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>317358.0</t>
+          <t>341670.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>762718.6</v>
+        <v>640798.4</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>611517.6</t>
+          <t>621223.7</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>155195.8</v>
+        <v>161045.58</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>151201</t>
+          <t>19574</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>84607.84086112375</t>
+          <t>80952.90549063997</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>87688.90110615233</t>
+          <t>60850.76095297909</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>317358.0</t>
+          <t>341670.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>246.67</t>
+          <t>247.92</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11279.0</t>
+          <t>5174.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>30.30</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,33 +11837,33 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11877,47 +11877,47 @@
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>5.54</v>
+        <v>2.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>22.31</v>
+        <v>23.89</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>47.48</v>
+        <v>48.42</v>
       </c>
       <c r="BA24" t="n">
-        <v>46.11</v>
+        <v>46.35</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>105.80</t>
+          <t>80.10</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>3.96</v>
+        <v>4.33</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-85.89</t>
+          <t>-82.35</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>717582.0165517242</t>
+          <t>717289.3285123967</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>705524.0</t>
+          <t>317358.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>770207.6</v>
+        <v>762718.6</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>591103.1</t>
+          <t>611517.6</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>149283.02</v>
+        <v>155195.8</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>179104</t>
+          <t>151201</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>84047.64808930038</t>
+          <t>84607.84086112375</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>125502.2119997515</t>
+          <t>87688.90110615233</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>705524.0</t>
+          <t>317358.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>246.67</t>
+          <t>247.92</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,17 +12102,17 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8858.0</t>
+          <t>11279.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>30.30</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12364,47 +12364,47 @@
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>9.699999999999999</v>
+        <v>5.54</v>
       </c>
       <c r="AV25" t="n">
-        <v>18.59</v>
+        <v>22.31</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>55.23999999999999</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>46.58</v>
+        <v>47.48</v>
       </c>
       <c r="BA25" t="n">
-        <v>45.89</v>
+        <v>46.11</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>142.06</t>
+          <t>105.80</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>3.42</v>
+        <v>3.96</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-89.62</t>
+          <t>-85.89</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>717582.0165517242</t>
+          <t>717289.3285123967</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>531651.0</t>
+          <t>705524.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>665029.6</v>
+        <v>770207.6</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>523057.5</t>
+          <t>591103.1</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>135986.22</v>
+        <v>149283.02</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>141972</t>
+          <t>179104</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>76510.45465103655</t>
+          <t>84047.64808930038</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>133449.7914191877</t>
+          <t>125502.2119997515</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>531651.0</t>
+          <t>705524.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,22 +12524,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>246.67</t>
+          <t>247.92</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
+          <t>65.1</t>
+        </is>
+      </c>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>58.6</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
           <t>61.3</t>
-        </is>
-      </c>
-      <c r="CS25" t="inlineStr">
-        <is>
-          <t>58.4</t>
-        </is>
-      </c>
-      <c r="CT25" t="inlineStr">
-        <is>
-          <t>60.6</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21925.0</t>
+          <t>8858.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>27.14</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>53.61</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12851,47 +12851,47 @@
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>13.88</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AV26" t="n">
-        <v>14.94</v>
+        <v>18.59</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-7.00</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>52.51000000000001</t>
+          <t>55.23999999999999</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>45.68</v>
+        <v>46.58</v>
       </c>
       <c r="BA26" t="n">
-        <v>45.66</v>
+        <v>45.89</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>203.00</t>
+          <t>142.06</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>2.76</v>
+        <v>3.42</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.91</v>
+        <v>1.41</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-93.31</t>
+          <t>-89.62</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>717582.0165517242</t>
+          <t>717289.3285123967</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>1307789.0</t>
+          <t>531651.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>613317.8</v>
+        <v>665029.6</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>472603.9</t>
+          <t>523057.5</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>125932.14</v>
+        <v>135986.22</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>140713</t>
+          <t>141972</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>66157.84796591816</t>
+          <t>76510.45465103655</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>158666.66232484</t>
+          <t>133449.7914191877</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>1307789.0</t>
+          <t>531651.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>246.67</t>
+          <t>247.92</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13113,7 +13113,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>17344.0</t>
+          <t>21925.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>74.90</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,33 +13298,33 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>53.61</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13334,51 +13334,51 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>88.55</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>12.34</v>
+        <v>13.88</v>
       </c>
       <c r="AV27" t="n">
-        <v>13.02</v>
+        <v>14.94</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.00</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>52.51000000000001</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>44.82</v>
+        <v>45.68</v>
       </c>
       <c r="BA27" t="n">
-        <v>45.45</v>
+        <v>45.66</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>49.11</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>336.90</t>
+          <t>203.00</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>1.96</v>
+        <v>2.76</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-96.70</t>
+          <t>-93.31</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>717582.0165517242</t>
+          <t>717289.3285123967</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>951271.0</t>
+          <t>1307789.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>601649</v>
+        <v>613317.8</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>343989.9</t>
+          <t>472603.9</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>100400.3</v>
+        <v>125932.14</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>257659</t>
+          <t>140713</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>49338.06353702328</t>
+          <t>66157.84796591816</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>105866.4542498846</t>
+          <t>158666.66232484</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>951271.0</t>
+          <t>1307789.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>246.67</t>
+          <t>247.92</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7063.0</t>
+          <t>17344.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>82.91</t>
+          <t>74.90</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>17.27</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13821,51 +13821,51 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>88.55</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>5.13</v>
+        <v>12.34</v>
       </c>
       <c r="AV28" t="n">
-        <v>11.96</v>
+        <v>13.02</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-7.86</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>50.65</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>44.01</v>
+        <v>44.82</v>
       </c>
       <c r="BA28" t="n">
-        <v>45.31</v>
+        <v>45.45</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>49.18</t>
+          <t>49.11</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>1603.09</t>
+          <t>336.90</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>1.21</v>
+        <v>1.96</v>
       </c>
       <c r="BE28" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-99.48</t>
+          <t>-96.70</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>717582.0165517242</t>
+          <t>717289.3285123967</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>354803.0</t>
+          <t>951271.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>460316.6</v>
+        <v>601649</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>251659.1</t>
+          <t>343989.9</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>82011.2</v>
+        <v>100400.3</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>208657</t>
+          <t>257659</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>39060.17431650303</t>
+          <t>49338.06353702328</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>64854.99791959545</t>
+          <t>105866.4542498846</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>354803.0</t>
+          <t>951271.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>246.67</t>
+          <t>247.92</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>276.56</t>
+          <t>271.03</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/印刷電路板.xlsx
+++ b/Result/checksun_type/印刷電路板.xlsx
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1118,22 +1118,22 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2024-12-09 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>8.41</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1159,106 +1159,106 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2.42</v>
+        <v>1.67</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.37</v>
+        <v>-0.65</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>42.13</t>
+          <t>42.44</t>
         </is>
       </c>
       <c r="AZ2" t="n">
         <v>42.72</v>
       </c>
       <c r="BA2" t="n">
-        <v>42.64</v>
+        <v>42.69</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>41.93</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-27.73</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.16</v>
+        <v>-0.09</v>
       </c>
       <c r="BE2" t="n">
         <v>-0.12</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-102.77</t>
+          <t>-108.78</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2025/08/27</t>
+          <t>2026/01/07</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>76527.58884297521</t>
+          <t>16441.58913934427</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>6398.0</t>
+          <t>5279.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>5052.6</v>
+        <v>5149.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>4126.7</t>
+          <t>4415.8</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>5396.04</v>
+        <v>5414.12</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>733</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-65.79690900617473</t>
+          <t>11.88953944763351</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>447.9319098097476</t>
+          <t>439.1650059435788</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>6398.0</t>
+          <t>5279.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2024-12-09 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,116 +1636,116 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>67.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.45</v>
+        <v>2.42</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.88</v>
+        <v>-1.37</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>42.74</v>
+        <v>42.72</v>
       </c>
       <c r="BA3" t="n">
-        <v>42.58</v>
+        <v>42.64</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>41.93</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-109.73</t>
+          <t>-27.73</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.24</v>
+        <v>-0.16</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2025/08/27</t>
+          <t>2026/01/07</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>76527.58884297521</t>
+          <t>16441.58913934427</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>7093.0</t>
+          <t>6398.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>4432.8</v>
+        <v>5052.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>3641.8</t>
+          <t>4126.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>5324.22</v>
+        <v>5396.04</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>925</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-159.2021487908879</t>
+          <t>-65.79690900617473</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>324.5656328396403</t>
+          <t>447.9319098097476</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>7093.0</t>
+          <t>6398.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2092,22 +2092,22 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2024-12-09 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,45 +2123,45 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>67.86</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.41</v>
+        <v>1.45</v>
       </c>
       <c r="AV4" t="n">
-        <v>-2.21</v>
+        <v>-1.88</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>42.82</v>
+        <v>42.74</v>
       </c>
       <c r="BA4" t="n">
-        <v>42.55</v>
+        <v>42.58</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -2170,69 +2170,69 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-237.95</t>
+          <t>-109.73</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.28</v>
+        <v>-0.24</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-101.87</t>
+          <t>-108.63</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2025/08/27</t>
+          <t>2026/01/07</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>76527.58884297521</t>
+          <t>16441.58913934427</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>4588.0</t>
+          <t>7093.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>4106.8</v>
+        <v>4432.8</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>3135.4</t>
+          <t>3641.8</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>5210.02</v>
+        <v>5324.22</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>791</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-247.1599272691658</t>
+          <t>-159.2021487908879</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>62.27217885235677</t>
+          <t>324.5656328396403</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>4588.0</t>
+          <t>7093.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,92 +2509,92 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-18.18</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>46.1</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025/04/11</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>43.8</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>42.05</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>7.59</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
           <t>-0.60</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-18.18</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>46.1</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/04/11</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>42.05</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>3.93</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>-0.36</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,45 +2610,45 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
           <t>3.57</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
       <c r="AU5" t="n">
-        <v>-0.88</v>
+        <v>-0.41</v>
       </c>
       <c r="AV5" t="n">
-        <v>-2.02</v>
+        <v>-2.21</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>42.89</v>
+        <v>42.82</v>
       </c>
       <c r="BA5" t="n">
-        <v>42.53</v>
+        <v>42.55</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -2657,69 +2657,69 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-616.22</t>
+          <t>-237.95</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-100.76</t>
+          <t>-106.26</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2025/08/27</t>
+          <t>2026/01/07</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>76527.58884297521</t>
+          <t>16441.58913934427</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>2390.0</t>
+          <t>4588.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>3455.4</v>
+        <v>4106.8</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>2936.2</t>
+          <t>3135.4</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>5165.48</v>
+        <v>5210.02</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>971</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-303.4203102003517</t>
+          <t>-247.1599272691658</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-46.26390465991744</t>
+          <t>62.27217885235677</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>2390.0</t>
+          <t>4588.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
+          <t>41.65</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>42.05</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
           <t>41.6</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>41.85</t>
-        </is>
-      </c>
-      <c r="CS5" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
-      </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3066,22 +3066,22 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2024-12-09 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,45 +3097,45 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.42</v>
+        <v>-0.88</v>
       </c>
       <c r="AV6" t="n">
-        <v>-1.77</v>
+        <v>-2.02</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>42.96</v>
+        <v>42.89</v>
       </c>
       <c r="BA6" t="n">
-        <v>42.52</v>
+        <v>42.53</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -3144,69 +3144,69 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1098.80</t>
+          <t>-616.22</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.18</v>
+        <v>-0.24</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-99.59</t>
+          <t>-102.54</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2025/08/27</t>
+          <t>2026/01/07</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>76527.58884297521</t>
+          <t>16441.58913934427</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>4794.0</t>
+          <t>2390.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>3682</v>
+        <v>3455.4</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>2940.4</t>
+          <t>2936.2</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>5156.86</v>
+        <v>5165.48</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>519</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-350.1760202986125</t>
+          <t>-303.4203102003517</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>35.83682977468789</t>
+          <t>-46.26390465991744</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>4794.0</t>
+          <t>2390.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,42 +3383,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-1.43</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>41.6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>42.2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3553,22 +3553,22 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2024-12-09 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3598,102 +3598,102 @@
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.66</v>
+        <v>-1.42</v>
       </c>
       <c r="AV7" t="n">
-        <v>-1.33</v>
+        <v>-1.77</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>43.05</v>
+        <v>42.96</v>
       </c>
       <c r="BA7" t="n">
-        <v>42.5</v>
+        <v>42.52</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-244.02</t>
+          <t>-1098.80</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.1</v>
+        <v>-0.18</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-98.47</t>
+          <t>-98.63</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2025/08/27</t>
+          <t>2026/01/07</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>76527.58884297521</t>
+          <t>16441.58913934427</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>3299.0</t>
+          <t>4794.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>3200.8</v>
+        <v>3682</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>2720.2</t>
+          <t>2940.4</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>5152.92</v>
+        <v>5156.86</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>741</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-420.3601748573943</t>
+          <t>-350.1760202986125</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-105.7277220964011</t>
+          <t>35.83682977468789</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>3299.0</t>
+          <t>4794.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>17.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2024-12-09 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4085,31 +4085,31 @@
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.99</v>
+        <v>-0.66</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.24</v>
+        <v>-1.33</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>42.48</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>43.15</v>
+        <v>43.05</v>
       </c>
       <c r="BA8" t="n">
-        <v>42.47</v>
+        <v>42.5</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
@@ -4118,69 +4118,69 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-147.29</t>
+          <t>-244.02</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-97.53</t>
+          <t>-94.86</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2025/08/27</t>
+          <t>2026/01/07</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>76527.58884297521</t>
+          <t>16441.58913934427</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>5463.0</t>
+          <t>3299.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>2850.8</v>
+        <v>3200.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>2592.2</t>
+          <t>2720.2</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>5117.16</v>
+        <v>5152.92</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>480</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-477.5660753593931</t>
+          <t>-420.3601748573943</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-144.0082346945132</t>
+          <t>-105.7277220964011</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>5463.0</t>
+          <t>3299.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4527,22 +4527,22 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2024-12-09 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4568,106 +4568,106 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.7</v>
+        <v>-0.99</v>
       </c>
       <c r="AV9" t="n">
-        <v>-1.01</v>
+        <v>-1.24</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>43.19</v>
+        <v>43.16</v>
       </c>
       <c r="BA9" t="n">
-        <v>42.42</v>
+        <v>42.47</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-94.73</t>
+          <t>-147.29</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-96.62</t>
+          <t>-91.73</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2025/08/27</t>
+          <t>2026/01/07</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>76527.58884297521</t>
+          <t>16441.58913934427</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>1331.0</t>
+          <t>5463.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>2164</v>
+        <v>2850.8</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>2415.9</t>
+          <t>2592.2</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>5055.46</v>
+        <v>5117.16</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-251</t>
+          <t>258</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-538.2129554802804</t>
+          <t>-477.5660753593931</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-425.4086728812981</t>
+          <t>-144.0082346945132</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>1331.0</t>
+          <t>5463.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.22</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2024-12-09 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5055,35 +5055,35 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.82</v>
+        <v>-0.7</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.68</v>
+        <v>-1.01</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>43.2</v>
+        <v>43.19</v>
       </c>
       <c r="BA10" t="n">
-        <v>42.37</v>
+        <v>42.42</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -5092,69 +5092,69 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-68.56</t>
+          <t>-94.73</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-95.82</t>
+          <t>-88.68</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2025/08/27</t>
+          <t>2026/01/07</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>76527.58884297521</t>
+          <t>16441.58913934427</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>3523.0</t>
+          <t>1331.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>2417</v>
+        <v>2164</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>2662.5</t>
+          <t>2415.9</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>5123.08</v>
+        <v>5055.46</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-245</t>
+          <t>-251</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-558.7228250437316</t>
+          <t>-538.2129554802804</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-369.5018462595149</t>
+          <t>-425.4086728812981</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>3523.0</t>
+          <t>1331.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5321,7 +5321,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5367.0</t>
+          <t>5213.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5451,34 +5451,34 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>279.0</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/04/28</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -5501,22 +5501,22 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2025-10-31 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>78.05</t>
+          <t>48.78</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>42.28</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>2.16</v>
+        <v>0.51</v>
       </c>
       <c r="AV11" t="n">
         <v>-3.29</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>314.2</t>
+          <t>313.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>324.88</v>
+        <v>324.05</v>
       </c>
       <c r="BA11" t="n">
-        <v>324.08</v>
+        <v>324.42</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>318.91</t>
+          <t>318.66</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-91.62</t>
+          <t>-62.93</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-3.48</v>
+        <v>-3.51</v>
       </c>
       <c r="BE11" t="n">
-        <v>-1.82</v>
+        <v>-2.15</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-110.56</t>
+          <t>-112.53</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>1504487.785123967</t>
+          <t>1941070.057377049</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>1701023.0</t>
+          <t>1642990.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>1263249.8</v>
+        <v>1495553.4</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1220360.3</t>
+          <t>1275148.3</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>2598674.62</v>
+        <v>2604369.62</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>42889</t>
+          <t>220405</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-257554.686217077</t>
+          <t>-243431.6150366727</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-212041.4124861672</t>
+          <t>-165754.7235444486</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>1701023.0</t>
+          <t>1642990.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29287</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>305.5</t>
+          <t>323.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>305.0</t>
+          <t>307.0</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3223.0</t>
+          <t>5367.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>305.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,29 +5943,29 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>279.0</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>2025/04/28</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -5988,22 +5988,22 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2025-10-31 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,168 +6014,168 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>78.05</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-2.87</v>
+        <v>2.16</v>
       </c>
       <c r="AV12" t="n">
-        <v>-3.61</v>
+        <v>-3.29</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>314.2</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>324.88</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>324.08</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>318.91</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-91.62</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>-110.56</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>1941070.057377049</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>1701023.0</t>
+        </is>
+      </c>
+      <c r="BK12" t="n">
+        <v>1263249.8</v>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>1220360.3</t>
+        </is>
+      </c>
+      <c r="BM12" t="n">
+        <v>2598674.62</v>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>42889</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-257554.686217077</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-212041.4124861672</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>1701023.0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>306.0</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>高技</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>高技</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>314.0</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>325.75</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>323.37</v>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>318.96</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-185.73</t>
-        </is>
-      </c>
-      <c r="BD12" t="n">
-        <v>-4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>17.2</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-108.14</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>1504487.785123967</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>986882.0</t>
-        </is>
-      </c>
-      <c r="BK12" t="n">
-        <v>1051406.4</v>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>1163051.3</t>
-        </is>
-      </c>
-      <c r="BM12" t="n">
-        <v>2582295.04</v>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-111644</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-265829.8268954243</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-276810.167671259</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>986882.0</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>306.0</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>高技</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>高技</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
       <c r="CA12" t="inlineStr">
         <is>
           <t>0.8245111470917923</t>
@@ -6193,22 +6193,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29287</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>311.0</t>
+          <t>305.5</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>314.5</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>299.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>305.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4451.0</t>
+          <t>3223.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,29 +6430,29 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AF13" t="inlineStr">
         <is>
           <t>279.0</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>2025/04/28</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
       <c r="AG13" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -6475,22 +6475,22 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2025-10-31 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,12 +6501,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6516,51 +6516,51 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-2.74</v>
+        <v>-2.87</v>
       </c>
       <c r="AV13" t="n">
-        <v>-2.88</v>
+        <v>-3.61</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>317.7</t>
+          <t>314.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>327.12</v>
+        <v>325.75</v>
       </c>
       <c r="BA13" t="n">
-        <v>322.85</v>
+        <v>323.37</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>319.5</t>
+          <t>318.96</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-296.96</t>
+          <t>-185.73</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-2.98</v>
+        <v>-4</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.75</v>
+        <v>-1.4</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-104.36</t>
+          <t>-108.14</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1504487.785123967</t>
+          <t>1941070.057377049</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>1386639.0</t>
+          <t>986882.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>1046928.2</v>
+        <v>1051406.4</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1156826.9</t>
+          <t>1163051.3</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>2577472.64</v>
+        <v>2582295.04</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-109898</t>
+          <t>-111644</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-263833.401299818</t>
+          <t>-265829.8268954243</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-282935.7762331311</t>
+          <t>-276810.167671259</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>1386639.0</t>
+          <t>986882.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29287</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>319.0</t>
+          <t>311.0</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>314.5</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>307.5</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5448.0</t>
+          <t>4451.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>317.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,29 +6917,29 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AF14" t="inlineStr">
         <is>
           <t>279.0</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>2025/04/28</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
       <c r="AG14" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -6962,22 +6962,22 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2025-10-31 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>51.19</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-1.25</v>
+        <v>-2.74</v>
       </c>
       <c r="AV14" t="n">
-        <v>-2.27</v>
+        <v>-2.88</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>317.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>328.45</v>
+        <v>327.12</v>
       </c>
       <c r="BA14" t="n">
-        <v>322.49</v>
+        <v>322.85</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>319.69</t>
+          <t>319.5</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-953.47</t>
+          <t>-296.96</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-2.03</v>
+        <v>-2.98</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.19</v>
+        <v>-0.75</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-101.12</t>
+          <t>-104.36</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1504487.785123967</t>
+          <t>1941070.057377049</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>1760233.0</t>
+          <t>1386639.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>1066636.2</v>
+        <v>1046928.2</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1150711.7</t>
+          <t>1156826.9</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>2566636.08</v>
+        <v>2577472.64</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-84075</t>
+          <t>-109898</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-260360.2422210338</t>
+          <t>-263833.401299818</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-324412.9035989079</t>
+          <t>-282935.7762331311</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>1760233.0</t>
+          <t>1386639.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29287</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7237,17 +7237,17 @@
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>317.0</t>
+          <t>307.5</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>317.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1510.0</t>
+          <t>5448.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>319.0</t>
+          <t>317.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,29 +7404,29 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AF15" t="inlineStr">
         <is>
           <t>279.0</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>2025/04/28</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
       <c r="AG15" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -7449,22 +7449,22 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2025-10-31 00:00:00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>53.57</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>51.19</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-1.15</v>
+        <v>-1.25</v>
       </c>
       <c r="AV15" t="n">
-        <v>-2.36</v>
+        <v>-2.27</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>322.7</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>330.5</v>
+        <v>328.45</v>
       </c>
       <c r="BA15" t="n">
-        <v>321.92</v>
+        <v>322.49</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>319.66</t>
+          <t>319.69</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-705.26</t>
+          <t>-953.47</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-1.62</v>
+        <v>-2.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.27</v>
+        <v>-0.19</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-98.45</t>
+          <t>-101.12</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1504487.785123967</t>
+          <t>1941070.057377049</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>481472.0</t>
+          <t>1760233.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>1054743.2</v>
+        <v>1066636.2</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1385012.3</t>
+          <t>1150711.7</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>2545738.9</v>
+        <v>2566636.08</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-330269</t>
+          <t>-84075</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-248714.3037886931</t>
+          <t>-260360.2422210338</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-412107.6961357708</t>
+          <t>-324412.9035989079</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>481472.0</t>
+          <t>1760233.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7654,22 +7654,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29287</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>321.5</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>316.5</t>
+          <t>317.0</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>319.0</t>
+          <t>317.0</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2001.0</t>
+          <t>1510.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.28</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,29 +7891,29 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>279.0</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>2025/04/28</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
       <c r="AG16" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -7936,22 +7936,22 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2025-10-31 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>60.71</t>
+          <t>53.57</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.15</v>
       </c>
       <c r="AV16" t="n">
-        <v>-3.18</v>
+        <v>-2.36</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>322.6</t>
+          <t>322.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>333.2</v>
+        <v>330.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>321.29</v>
+        <v>321.92</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>319.52</t>
+          <t>319.66</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-271.33</t>
+          <t>-705.26</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-1.27</v>
+        <v>-1.62</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.74</v>
+        <v>0.27</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-95.71</t>
+          <t>-98.45</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1504487.785123967</t>
+          <t>1941070.057377049</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>641806.0</t>
+          <t>481472.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>1177470.8</v>
+        <v>1054743.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1764696.2</t>
+          <t>1385012.3</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>2550748.96</v>
+        <v>2545738.9</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-587225</t>
+          <t>-330269</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-219006.4142710426</t>
+          <t>-248714.3037886931</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-385657.7320407256</t>
+          <t>-412107.6961357708</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>641806.0</t>
+          <t>481472.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29287</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>324.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>324.5</t>
+          <t>321.5</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>318.0</t>
+          <t>316.5</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>319.0</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2944.0</t>
+          <t>2001.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,167 +8278,167 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>-1.59</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-33.28</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>354.0</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>316.0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>320.5</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>304.0</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>16.45</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025/05/22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>194.0</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>316.0</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>304.0</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
           <t>-0.78</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-33.86</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>354.0</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>316.0</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>320.5</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>304.0</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>16.45</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025/05/22</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>194.0</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>2025/04/28</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>316.0</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>304.0</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>5.92</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>-2.63</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>45.77</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>0.62</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>-4</v>
+        <v>-3.18</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>321.5</t>
+          <t>322.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>334.9</v>
+        <v>333.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>320.76</v>
+        <v>321.29</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>319.49</t>
+          <t>319.52</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-172.52</t>
+          <t>-271.33</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.9</v>
+        <v>-1.27</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.24</v>
+        <v>0.74</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-92.79</t>
+          <t>-95.71</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1504487.785123967</t>
+          <t>1941070.057377049</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>964491.0</t>
+          <t>641806.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>1274696.2</v>
+        <v>1177470.8</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1927234.5</t>
+          <t>1764696.2</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>2556586.22</v>
+        <v>2550748.96</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-652538</t>
+          <t>-587225</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-188706.1746765548</t>
+          <t>-219006.4142710426</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-351277.2214749211</t>
+          <t>-385657.7320407256</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>964491.0</t>
+          <t>641806.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29287</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>328.5</t>
+          <t>324.5</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>324.5</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>323.5</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4557.0</t>
+          <t>2944.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>325.5</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-39.16</t>
+          <t>-33.86</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,29 +8865,29 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>279.0</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>2025/04/28</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
       <c r="AG18" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -8910,22 +8910,22 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2025-10-31 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>2.01</v>
+        <v>0.62</v>
       </c>
       <c r="AV18" t="n">
-        <v>-4.87</v>
+        <v>-4</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>319.1</t>
+          <t>321.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>335.45</v>
+        <v>334.9</v>
       </c>
       <c r="BA18" t="n">
-        <v>320.26</v>
+        <v>320.76</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>319.48</t>
+          <t>319.49</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-143.66</t>
+          <t>-172.52</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.77</v>
+        <v>-0.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-89.68</t>
+          <t>-92.79</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1504487.785123967</t>
+          <t>1941070.057377049</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>1485179.0</t>
+          <t>964491.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>1266725.6</v>
+        <v>1274696.2</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>2082194.3</t>
+          <t>1927234.5</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>2560207.9</v>
+        <v>2556586.22</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-815468</t>
+          <t>-652538</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-159147.8025313973</t>
+          <t>-188706.1746765548</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-324189.9841853818</t>
+          <t>-351277.2214749211</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>1485179.0</t>
+          <t>964491.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29287</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>329.5</t>
+          <t>328.5</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>331.5</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>325.5</t>
+          <t>323.5</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5199.0</t>
+          <t>4557.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-45.44</t>
+          <t>-39.16</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9352,29 +9352,29 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
+          <t>2026/01/07</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AF19" t="inlineStr">
         <is>
           <t>279.0</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>2025/04/28</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
       <c r="AG19" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -9397,22 +9397,22 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2025-10-31 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,12 +9423,12 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9438,51 +9438,51 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>2.81</v>
+        <v>2.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>-5.48</v>
+        <v>-4.87</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>316.6</t>
+          <t>319.1</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>334.95</v>
+        <v>335.45</v>
       </c>
       <c r="BA19" t="n">
-        <v>319.43</v>
+        <v>320.26</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>319.18</t>
+          <t>319.48</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-133.52</t>
+          <t>-143.66</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.77</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.41</v>
+        <v>1.77</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-85.98</t>
+          <t>-89.68</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1504487.785123967</t>
+          <t>1941070.057377049</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>1700768.0</t>
+          <t>1485179.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>1234787.2</v>
+        <v>1266725.6</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>2263207.5</t>
+          <t>2082194.3</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>2579630.12</v>
+        <v>2560207.9</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-1028420</t>
+          <t>-815468</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-129140.1331397637</t>
+          <t>-159147.8025313973</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-329703.7171937048</t>
+          <t>-324189.9841853818</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>1700768.0</t>
+          <t>1485179.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29287</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,17 +9667,17 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
+          <t>329.5</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>331.5</t>
+        </is>
+      </c>
+      <c r="CS19" t="inlineStr">
+        <is>
           <t>321.0</t>
-        </is>
-      </c>
-      <c r="CR19" t="inlineStr">
-        <is>
-          <t>331.0</t>
-        </is>
-      </c>
-      <c r="CS19" t="inlineStr">
-        <is>
-          <t>320.5</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
@@ -9704,7 +9704,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-7.86</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5573.0</t>
+          <t>5201.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-45.14</t>
+          <t>-45.43</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9884,22 +9884,22 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2024-11-08 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>71.48</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>0.13</v>
+        <v>-5.57</v>
       </c>
       <c r="AV20" t="n">
-        <v>14.71</v>
+        <v>10.96</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>59.41999999999999</t>
+          <t>58.14</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>51.8</v>
+        <v>52.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>47.01</v>
+        <v>47.12</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>49.13</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>4.25</v>
+        <v>3.81</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-74.13</t>
+          <t>-73.72</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,48 +9988,48 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>717289.3285123967</t>
+          <t>1032424.294057377</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>336727.0</t>
+          <t>292688.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>291130</v>
+        <v>286196</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>530668.8</t>
+          <t>524457.3</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>174983.32</v>
+        <v>180047.34</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-239538</t>
+          <t>-238261</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>54782.7364856178</t>
+          <t>45712.3638201717</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>3952.116148940462</t>
+          <t>-4174.685839781829</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>336727.0</t>
+          <t>292688.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -10094,17 +10094,17 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>247.92</t>
+          <t>228.75</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10149,27 +10149,27 @@
       </c>
       <c r="CP20" t="inlineStr">
         <is>
-          <t>通信網路業平上櫃</t>
+          <t>通信網路業右下上櫃</t>
         </is>
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3551.0</t>
+          <t>5573.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-29.14</t>
+          <t>-45.14</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10371,22 +10371,22 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2024-11-08 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>77.89</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>79.78</t>
+          <t>71.48</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.97</v>
+        <v>0.13</v>
       </c>
       <c r="AV21" t="n">
-        <v>17.42</v>
+        <v>14.71</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-4.70</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>59.77999999999999</t>
+          <t>59.41999999999999</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>50.91</v>
+        <v>51.8</v>
       </c>
       <c r="BA21" t="n">
-        <v>46.81</v>
+        <v>47.01</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.13</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="BE21" t="n">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-75.47</t>
+          <t>-74.13</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,48 +10475,48 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>717289.3285123967</t>
+          <t>1032424.294057377</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>206305.0</t>
+          <t>336727.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>364889.4</v>
+        <v>291130</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>514959.5</t>
+          <t>530668.8</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>169166.64</v>
+        <v>174983.32</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-150070</t>
+          <t>-239538</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>64024.66745592276</t>
+          <t>54782.7364856178</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>10702.22198465298</t>
+          <t>3952.116148940462</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>206305.0</t>
+          <t>336727.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -10576,22 +10576,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>247.92</t>
+          <t>228.75</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10636,27 +10636,27 @@
       </c>
       <c r="CP21" t="inlineStr">
         <is>
-          <t>通信網路業平上櫃</t>
+          <t>通信網路業右下上櫃</t>
         </is>
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>62.7</t>
+        </is>
+      </c>
+      <c r="CS21" t="inlineStr">
+        <is>
           <t>58.5</t>
         </is>
       </c>
-      <c r="CR21" t="inlineStr">
+      <c r="CT21" t="inlineStr">
         <is>
           <t>59.5</t>
-        </is>
-      </c>
-      <c r="CS21" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="CT21" t="inlineStr">
-        <is>
-          <t>59.2</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4357.0</t>
+          <t>3551.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-17.58</t>
+          <t>-29.14</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10858,22 +10858,22 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2024-11-08 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>77.89</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>87.15</t>
+          <t>79.78</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-3.26</v>
+        <v>-0.97</v>
       </c>
       <c r="AV22" t="n">
-        <v>19.98</v>
+        <v>17.42</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-4.70</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>60.06</t>
+          <t>59.77999999999999</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>50.06</v>
+        <v>50.91</v>
       </c>
       <c r="BA22" t="n">
-        <v>46.65</v>
+        <v>46.81</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>49.11</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="BE22" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-77.22</t>
+          <t>-75.47</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,48 +10962,48 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>717289.3285123967</t>
+          <t>1032424.294057377</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>253590.0</t>
+          <t>206305.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>429958.6</v>
+        <v>364889.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>521638.2</t>
+          <t>514959.5</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>165471.38</v>
+        <v>169166.64</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-91679</t>
+          <t>-150070</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>73719.65754160818</t>
+          <t>64024.66745592276</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>33936.79382193333</t>
+          <t>10702.22198465298</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>253590.0</t>
+          <t>206305.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11063,22 +11063,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>247.92</t>
+          <t>228.75</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11123,27 +11123,27 @@
       </c>
       <c r="CP22" t="inlineStr">
         <is>
-          <t>通信網路業平上櫃</t>
+          <t>通信網路業右下上櫃</t>
         </is>
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5615.0</t>
+          <t>4357.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,74 +11190,74 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-5.83</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.67</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-17.58</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2024-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2024-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>59.0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2024-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2024-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>59.0</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>138.5</t>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11345,22 +11345,22 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2024-11-08 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>83.97</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>94.66</t>
+          <t>87.15</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-2.32</v>
+        <v>-3.26</v>
       </c>
       <c r="AV23" t="n">
-        <v>22.6</v>
+        <v>19.98</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.06</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>49.26</v>
+        <v>50.06</v>
       </c>
       <c r="BA23" t="n">
-        <v>46.51</v>
+        <v>46.65</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.11</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>56.70</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-79.44</t>
+          <t>-77.22</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,48 +11449,48 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>717289.3285123967</t>
+          <t>1032424.294057377</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>341670.0</t>
+          <t>253590.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>640798.4</v>
+        <v>429958.6</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>621223.7</t>
+          <t>521638.2</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>161045.58</v>
+        <v>165471.38</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>19574</t>
+          <t>-91679</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>80952.90549063997</t>
+          <t>73719.65754160818</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>60850.76095297909</t>
+          <t>33936.79382193333</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>341670.0</t>
+          <t>253590.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>247.92</t>
+          <t>228.75</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11610,27 +11610,27 @@
       </c>
       <c r="CP23" t="inlineStr">
         <is>
-          <t>通信網路業平上櫃</t>
+          <t>通信網路業右下上櫃</t>
         </is>
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5174.0</t>
+          <t>5615.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,27 +11687,27 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11832,22 +11832,22 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2024-11-08 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,50 +11858,50 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.97</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.66</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>2.2</v>
+        <v>-2.32</v>
       </c>
       <c r="AV24" t="n">
-        <v>23.89</v>
+        <v>22.6</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>48.42</v>
+        <v>49.26</v>
       </c>
       <c r="BA24" t="n">
-        <v>46.35</v>
+        <v>46.51</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
@@ -11910,14 +11910,14 @@
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>80.10</t>
+          <t>56.70</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>4.33</v>
+        <v>4.39</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-82.35</t>
+          <t>-79.44</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,48 +11936,48 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>717289.3285123967</t>
+          <t>1032424.294057377</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>317358.0</t>
+          <t>341670.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>762718.6</v>
+        <v>640798.4</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>611517.6</t>
+          <t>621223.7</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>155195.8</v>
+        <v>161045.58</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>151201</t>
+          <t>19574</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>84607.84086112375</t>
+          <t>80952.90549063997</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>87688.90110615233</t>
+          <t>60850.76095297909</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>317358.0</t>
+          <t>341670.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>247.92</t>
+          <t>228.75</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12097,27 +12097,27 @@
       </c>
       <c r="CP24" t="inlineStr">
         <is>
-          <t>通信網路業平上櫃</t>
+          <t>通信網路業右下上櫃</t>
         </is>
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>11279.0</t>
+          <t>5174.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-11.66</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30.30</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12319,38 +12319,38 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2024-11-08 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12364,47 +12364,47 @@
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>5.54</v>
+        <v>2.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>22.31</v>
+        <v>23.89</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>47.48</v>
+        <v>48.42</v>
       </c>
       <c r="BA25" t="n">
-        <v>46.11</v>
+        <v>46.35</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>105.80</t>
+          <t>80.10</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>3.96</v>
+        <v>4.33</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-85.89</t>
+          <t>-82.35</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>717289.3285123967</t>
+          <t>1032424.294057377</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>705524.0</t>
+          <t>317358.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>770207.6</v>
+        <v>762718.6</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>591103.1</t>
+          <t>611517.6</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>149283.02</v>
+        <v>155195.8</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>179104</t>
+          <t>151201</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>84047.64808930038</t>
+          <t>84607.84086112375</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>125502.2119997515</t>
+          <t>87688.90110615233</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>705524.0</t>
+          <t>317358.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>247.92</t>
+          <t>228.75</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12584,22 +12584,22 @@
       </c>
       <c r="CP25" t="inlineStr">
         <is>
-          <t>通信網路業平上櫃</t>
+          <t>通信網路業右下上櫃</t>
         </is>
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8858.0</t>
+          <t>11279.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-11.66</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>27.14</t>
+          <t>30.30</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12806,22 +12806,22 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2024-11-08 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12851,47 +12851,47 @@
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>9.699999999999999</v>
+        <v>5.54</v>
       </c>
       <c r="AV26" t="n">
-        <v>18.59</v>
+        <v>22.31</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>55.23999999999999</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>46.58</v>
+        <v>47.48</v>
       </c>
       <c r="BA26" t="n">
-        <v>45.89</v>
+        <v>46.11</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>142.06</t>
+          <t>105.80</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>3.42</v>
+        <v>3.96</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-89.62</t>
+          <t>-85.89</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>717289.3285123967</t>
+          <t>1032424.294057377</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>531651.0</t>
+          <t>705524.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>665029.6</v>
+        <v>770207.6</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>523057.5</t>
+          <t>591103.1</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>135986.22</v>
+        <v>149283.02</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>141972</t>
+          <t>179104</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>76510.45465103655</t>
+          <t>84047.64808930038</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>133449.7914191877</t>
+          <t>125502.2119997515</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>531651.0</t>
+          <t>705524.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>247.92</t>
+          <t>228.75</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13071,27 +13071,27 @@
       </c>
       <c r="CP26" t="inlineStr">
         <is>
-          <t>通信網路業平上櫃</t>
+          <t>通信網路業右下上櫃</t>
         </is>
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
+          <t>65.1</t>
+        </is>
+      </c>
+      <c r="CS26" t="inlineStr">
+        <is>
+          <t>58.6</t>
+        </is>
+      </c>
+      <c r="CT26" t="inlineStr">
+        <is>
           <t>61.3</t>
-        </is>
-      </c>
-      <c r="CS26" t="inlineStr">
-        <is>
-          <t>58.4</t>
-        </is>
-      </c>
-      <c r="CT26" t="inlineStr">
-        <is>
-          <t>60.6</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>21925.0</t>
+          <t>8858.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-10.38</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>27.14</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13293,22 +13293,22 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2024-11-08 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>53.61</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13338,47 +13338,47 @@
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>13.88</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AV27" t="n">
-        <v>14.94</v>
+        <v>18.59</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-7.00</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>52.51000000000001</t>
+          <t>55.23999999999999</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>45.68</v>
+        <v>46.58</v>
       </c>
       <c r="BA27" t="n">
-        <v>45.66</v>
+        <v>45.89</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>203.00</t>
+          <t>142.06</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>2.76</v>
+        <v>3.42</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.91</v>
+        <v>1.41</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-93.31</t>
+          <t>-89.62</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>717289.3285123967</t>
+          <t>1032424.294057377</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>1307789.0</t>
+          <t>531651.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>613317.8</v>
+        <v>665029.6</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>472603.9</t>
+          <t>523057.5</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>125932.14</v>
+        <v>135986.22</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>140713</t>
+          <t>141972</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>66157.84796591816</t>
+          <t>76510.45465103655</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>158666.66232484</t>
+          <t>133449.7914191877</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>1307789.0</t>
+          <t>531651.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>247.92</t>
+          <t>228.75</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13558,27 +13558,27 @@
       </c>
       <c r="CP27" t="inlineStr">
         <is>
-          <t>通信網路業平上櫃</t>
+          <t>通信網路業右下上櫃</t>
         </is>
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13600,7 +13600,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17344.0</t>
+          <t>21925.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>74.90</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13780,38 +13780,38 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2024-11-08 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>53.61</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13821,51 +13821,51 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>88.55</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>12.34</v>
+        <v>13.88</v>
       </c>
       <c r="AV28" t="n">
-        <v>13.02</v>
+        <v>14.94</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-7.00</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>52.51000000000001</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>44.82</v>
+        <v>45.68</v>
       </c>
       <c r="BA28" t="n">
-        <v>45.45</v>
+        <v>45.66</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>49.11</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>336.90</t>
+          <t>203.00</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>1.96</v>
+        <v>2.76</v>
       </c>
       <c r="BE28" t="n">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-96.70</t>
+          <t>-93.31</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>717289.3285123967</t>
+          <t>1032424.294057377</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>951271.0</t>
+          <t>1307789.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>601649</v>
+        <v>613317.8</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>343989.9</t>
+          <t>472603.9</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>100400.3</v>
+        <v>125932.14</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>257659</t>
+          <t>140713</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>49338.06353702328</t>
+          <t>66157.84796591816</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>105866.4542498846</t>
+          <t>158666.66232484</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>951271.0</t>
+          <t>1307789.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>247.92</t>
+          <t>228.75</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>271.03</t>
+          <t>265.4</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14045,27 +14045,27 @@
       </c>
       <c r="CP28" t="inlineStr">
         <is>
-          <t>通信網路業平上櫃</t>
+          <t>通信網路業右下上櫃</t>
         </is>
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
